--- a/data/dolar-ipc.xlsx
+++ b/data/dolar-ipc.xlsx
@@ -28,7 +28,7 @@
     <t xml:space="preserve">Dólar-compra</t>
   </si>
   <si>
-    <t xml:space="preserve">Dólar-venta</t>
+    <t xml:space="preserve">Dolar-venta</t>
   </si>
   <si>
     <t xml:space="preserve">TotalNacional-Nivelgeneral</t>
@@ -61,7 +61,7 @@
     <numFmt numFmtId="165" formatCode="mm/yy"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -90,13 +90,6 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="8"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b val="true"/>
@@ -161,7 +154,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -174,11 +167,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -186,7 +175,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -441,7 +430,7 @@
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
@@ -467,3600 +456,3628 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="n">
+      <c r="A2" s="3" t="n">
         <v>42736</v>
       </c>
-      <c r="B2" s="5" t="n">
+      <c r="B2" s="4" t="n">
         <v>-1.40632094560171</v>
       </c>
-      <c r="C2" s="5" t="n">
+      <c r="C2" s="4" t="n">
         <v>-1.37274611648145</v>
       </c>
-      <c r="D2" s="6" t="n">
+      <c r="D2" s="5" t="n">
         <v>1.6</v>
       </c>
-      <c r="E2" s="6" t="n">
+      <c r="E2" s="5" t="n">
         <v>1.3</v>
       </c>
-      <c r="F2" s="6" t="n">
+      <c r="F2" s="5" t="n">
         <v>1.8</v>
       </c>
-      <c r="G2" s="6" t="n">
+      <c r="G2" s="5" t="n">
         <v>1.6</v>
       </c>
-      <c r="H2" s="6" t="n">
+      <c r="H2" s="5" t="n">
         <v>1.7</v>
       </c>
-      <c r="I2" s="6" t="n">
+      <c r="I2" s="5" t="n">
         <v>1.7</v>
       </c>
-      <c r="J2" s="6" t="n">
+      <c r="J2" s="5" t="n">
         <v>2.6</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="n">
+      <c r="A3" s="3" t="n">
         <v>42767</v>
       </c>
-      <c r="B3" s="6" t="n">
+      <c r="B3" s="5" t="n">
         <v>-2.2416878914542</v>
       </c>
-      <c r="C3" s="6" t="n">
+      <c r="C3" s="5" t="n">
         <v>-2.18720748186682</v>
       </c>
-      <c r="D3" s="6" t="n">
+      <c r="D3" s="5" t="n">
         <v>2.1</v>
       </c>
-      <c r="E3" s="6" t="n">
+      <c r="E3" s="5" t="n">
         <v>2.5</v>
       </c>
-      <c r="F3" s="6" t="n">
+      <c r="F3" s="5" t="n">
         <v>1.7</v>
       </c>
-      <c r="G3" s="6" t="n">
+      <c r="G3" s="5" t="n">
         <v>2.1</v>
       </c>
-      <c r="H3" s="6" t="n">
+      <c r="H3" s="5" t="n">
         <v>1.8</v>
       </c>
-      <c r="I3" s="6" t="n">
+      <c r="I3" s="5" t="n">
         <v>1.5</v>
       </c>
-      <c r="J3" s="6" t="n">
+      <c r="J3" s="5" t="n">
         <v>1.7</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="n">
+      <c r="A4" s="3" t="n">
         <v>42795</v>
       </c>
-      <c r="B4" s="5" t="n">
+      <c r="B4" s="4" t="n">
         <v>-1.90724153763875</v>
       </c>
-      <c r="C4" s="5" t="n">
+      <c r="C4" s="4" t="n">
         <v>-1.85994202362656</v>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="D4" s="5" t="n">
         <v>2.4</v>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="E4" s="5" t="n">
         <v>2.4</v>
       </c>
-      <c r="F4" s="6" t="n">
+      <c r="F4" s="5" t="n">
         <v>2.2</v>
       </c>
-      <c r="G4" s="6" t="n">
+      <c r="G4" s="5" t="n">
         <v>3.2</v>
       </c>
-      <c r="H4" s="6" t="n">
+      <c r="H4" s="5" t="n">
         <v>2.4</v>
       </c>
-      <c r="I4" s="6" t="n">
+      <c r="I4" s="5" t="n">
         <v>2.6</v>
       </c>
-      <c r="J4" s="6" t="n">
+      <c r="J4" s="5" t="n">
         <v>2.1</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="n">
+      <c r="A5" s="3" t="n">
         <v>42826</v>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B5" s="4" t="n">
         <v>0.064164262708304</v>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C5" s="4" t="n">
         <v>0.0625586507734168</v>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="D5" s="5" t="n">
         <v>2.7</v>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="E5" s="5" t="n">
         <v>2.6</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="F5" s="5" t="n">
         <v>2.7</v>
       </c>
-      <c r="G5" s="6" t="n">
+      <c r="G5" s="5" t="n">
         <v>2.7</v>
       </c>
-      <c r="H5" s="6" t="n">
+      <c r="H5" s="5" t="n">
         <v>2.2</v>
       </c>
-      <c r="I5" s="6" t="n">
+      <c r="I5" s="5" t="n">
         <v>3.3</v>
       </c>
-      <c r="J5" s="6" t="n">
+      <c r="J5" s="5" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="n">
+      <c r="A6" s="3" t="n">
         <v>42856</v>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="4" t="n">
         <v>2.53338437761777</v>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C6" s="4" t="n">
         <v>2.47078659098754</v>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="D6" s="5" t="n">
         <v>1.4</v>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="E6" s="5" t="n">
         <v>1.3</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="F6" s="5" t="n">
         <v>1.5</v>
       </c>
-      <c r="G6" s="6" t="n">
+      <c r="G6" s="5" t="n">
         <v>1.5</v>
       </c>
-      <c r="H6" s="6" t="n">
+      <c r="H6" s="5" t="n">
         <v>1.9</v>
       </c>
-      <c r="I6" s="6" t="n">
+      <c r="I6" s="5" t="n">
         <v>1.7</v>
       </c>
-      <c r="J6" s="6" t="n">
+      <c r="J6" s="5" t="n">
         <v>1.7</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="n">
+      <c r="A7" s="3" t="n">
         <v>42887</v>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="4" t="n">
         <v>2.77538627821711</v>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C7" s="4" t="n">
         <v>2.70856160584423</v>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="D7" s="5" t="n">
         <v>1.2</v>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="E7" s="5" t="n">
         <v>1.4</v>
       </c>
-      <c r="F7" s="6" t="n">
+      <c r="F7" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G7" s="6" t="n">
+      <c r="G7" s="5" t="n">
         <v>0.9</v>
       </c>
-      <c r="H7" s="6" t="n">
+      <c r="H7" s="5" t="n">
         <v>1.4</v>
       </c>
-      <c r="I7" s="6" t="n">
+      <c r="I7" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="J7" s="6" t="n">
+      <c r="J7" s="5" t="n">
         <v>1.1</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="n">
+      <c r="A8" s="3" t="n">
         <v>42917</v>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="4" t="n">
         <v>7.10183937512719</v>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="C8" s="4" t="n">
         <v>7.16022905930232</v>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="D8" s="5" t="n">
         <v>1.7</v>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="E8" s="5" t="n">
         <v>1.7</v>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="F8" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="G8" s="6" t="n">
+      <c r="G8" s="5" t="n">
         <v>1.4</v>
       </c>
-      <c r="H8" s="6" t="n">
+      <c r="H8" s="5" t="n">
         <v>1.3</v>
       </c>
-      <c r="I8" s="6" t="n">
+      <c r="I8" s="5" t="n">
         <v>1.4</v>
       </c>
-      <c r="J8" s="6" t="n">
+      <c r="J8" s="5" t="n">
         <v>1.5</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="n">
+      <c r="A9" s="3" t="n">
         <v>42948</v>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="4" t="n">
         <v>1.01466484957433</v>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C9" s="4" t="n">
         <v>0.770928928336787</v>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="D9" s="5" t="n">
         <v>1.4</v>
       </c>
-      <c r="E9" s="6" t="n">
+      <c r="E9" s="5" t="n">
         <v>1.5</v>
       </c>
-      <c r="F9" s="6" t="n">
+      <c r="F9" s="5" t="n">
         <v>1.3</v>
       </c>
-      <c r="G9" s="6" t="n">
+      <c r="G9" s="5" t="n">
         <v>1.3</v>
       </c>
-      <c r="H9" s="6" t="n">
+      <c r="H9" s="5" t="n">
         <v>1.2</v>
       </c>
-      <c r="I9" s="6" t="n">
+      <c r="I9" s="5" t="n">
         <v>1.4</v>
       </c>
-      <c r="J9" s="6" t="n">
+      <c r="J9" s="5" t="n">
         <v>1.7</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="n">
+      <c r="A10" s="3" t="n">
         <v>42979</v>
       </c>
-      <c r="B10" s="5" t="n">
+      <c r="B10" s="4" t="n">
         <v>-1.81102855772884</v>
       </c>
-      <c r="C10" s="5" t="n">
+      <c r="C10" s="4" t="n">
         <v>-1.77093726179513</v>
       </c>
-      <c r="D10" s="6" t="n">
+      <c r="D10" s="5" t="n">
         <v>1.9</v>
       </c>
-      <c r="E10" s="6" t="n">
+      <c r="E10" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F10" s="6" t="n">
+      <c r="F10" s="5" t="n">
         <v>1.9</v>
       </c>
-      <c r="G10" s="6" t="n">
+      <c r="G10" s="5" t="n">
         <v>1.8</v>
       </c>
-      <c r="H10" s="6" t="n">
+      <c r="H10" s="5" t="n">
         <v>1.3</v>
       </c>
-      <c r="I10" s="6" t="n">
+      <c r="I10" s="5" t="n">
         <v>1.7</v>
       </c>
-      <c r="J10" s="6" t="n">
+      <c r="J10" s="5" t="n">
         <v>1.3</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="n">
+      <c r="A11" s="3" t="n">
         <v>43009</v>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B11" s="4" t="n">
         <v>1.07924932820228</v>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="C11" s="4" t="n">
         <v>1.05527221991597</v>
       </c>
-      <c r="D11" s="6" t="n">
+      <c r="D11" s="5" t="n">
         <v>1.5</v>
       </c>
-      <c r="E11" s="6" t="n">
+      <c r="E11" s="5" t="n">
         <v>1.3</v>
       </c>
-      <c r="F11" s="6" t="n">
+      <c r="F11" s="5" t="n">
         <v>1.7</v>
       </c>
-      <c r="G11" s="6" t="n">
+      <c r="G11" s="5" t="n">
         <v>1.9</v>
       </c>
-      <c r="H11" s="6" t="n">
+      <c r="H11" s="5" t="n">
         <v>1.5</v>
       </c>
-      <c r="I11" s="6" t="n">
+      <c r="I11" s="5" t="n">
         <v>1.7</v>
       </c>
-      <c r="J11" s="6" t="n">
+      <c r="J11" s="5" t="n">
         <v>1.6</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="n">
+      <c r="A12" s="3" t="n">
         <v>43040</v>
       </c>
-      <c r="B12" s="5" t="n">
+      <c r="B12" s="4" t="n">
         <v>-0.794105137281292</v>
       </c>
-      <c r="C12" s="5" t="n">
+      <c r="C12" s="4" t="n">
         <v>-0.776487539772654</v>
       </c>
-      <c r="D12" s="6" t="n">
+      <c r="D12" s="5" t="n">
         <v>1.4</v>
       </c>
-      <c r="E12" s="6" t="n">
+      <c r="E12" s="5" t="n">
         <v>1.2</v>
       </c>
-      <c r="F12" s="6" t="n">
+      <c r="F12" s="5" t="n">
         <v>1.6</v>
       </c>
-      <c r="G12" s="6" t="n">
+      <c r="G12" s="5" t="n">
         <v>1.3</v>
       </c>
-      <c r="H12" s="6" t="n">
+      <c r="H12" s="5" t="n">
         <v>1.5</v>
       </c>
-      <c r="I12" s="6" t="n">
+      <c r="I12" s="5" t="n">
         <v>1.6</v>
       </c>
-      <c r="J12" s="6" t="n">
+      <c r="J12" s="5" t="n">
         <v>1.5</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="n">
+      <c r="A13" s="3" t="n">
         <v>43070</v>
       </c>
-      <c r="B13" s="5" t="n">
+      <c r="B13" s="4" t="n">
         <v>7.24795725103841</v>
       </c>
-      <c r="C13" s="5" t="n">
+      <c r="C13" s="4" t="n">
         <v>7.0921226308346</v>
       </c>
-      <c r="D13" s="6" t="n">
+      <c r="D13" s="5" t="n">
         <v>3.1</v>
       </c>
-      <c r="E13" s="6" t="n">
+      <c r="E13" s="5" t="n">
         <v>3.4</v>
       </c>
-      <c r="F13" s="6" t="n">
+      <c r="F13" s="5" t="n">
         <v>3.1</v>
       </c>
-      <c r="G13" s="6" t="n">
+      <c r="G13" s="5" t="n">
         <v>2.3</v>
       </c>
-      <c r="H13" s="6" t="n">
+      <c r="H13" s="5" t="n">
         <v>2.2</v>
       </c>
-      <c r="I13" s="6" t="n">
+      <c r="I13" s="5" t="n">
         <v>3.3</v>
       </c>
-      <c r="J13" s="6" t="n">
+      <c r="J13" s="5" t="n">
         <v>2.5</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="n">
+      <c r="A14" s="3" t="n">
         <v>43101</v>
       </c>
-      <c r="B14" s="5" t="n">
+      <c r="B14" s="4" t="n">
         <v>3.48721257140201</v>
       </c>
-      <c r="C14" s="5" t="n">
+      <c r="C14" s="4" t="n">
         <v>3.41608541534728</v>
       </c>
-      <c r="D14" s="6" t="n">
+      <c r="D14" s="5" t="n">
         <v>1.8</v>
       </c>
-      <c r="E14" s="6" t="n">
+      <c r="E14" s="5" t="n">
         <v>1.6</v>
       </c>
-      <c r="F14" s="6" t="n">
+      <c r="F14" s="5" t="n">
         <v>1.9</v>
       </c>
-      <c r="G14" s="6" t="n">
+      <c r="G14" s="5" t="n">
         <v>1.9</v>
       </c>
-      <c r="H14" s="6" t="n">
+      <c r="H14" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="I14" s="6" t="n">
+      <c r="I14" s="5" t="n">
         <v>1.5</v>
       </c>
-      <c r="J14" s="6" t="n">
+      <c r="J14" s="5" t="n">
         <v>2.6</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="n">
+      <c r="A15" s="3" t="n">
         <v>43132</v>
       </c>
-      <c r="B15" s="5" t="n">
+      <c r="B15" s="4" t="n">
         <v>2.02538569044976</v>
       </c>
-      <c r="C15" s="5" t="n">
+      <c r="C15" s="4" t="n">
         <v>1.98517685527315</v>
       </c>
-      <c r="D15" s="6" t="n">
+      <c r="D15" s="5" t="n">
         <v>2.4</v>
       </c>
-      <c r="E15" s="6" t="n">
+      <c r="E15" s="5" t="n">
         <v>2.6</v>
       </c>
-      <c r="F15" s="6" t="n">
+      <c r="F15" s="5" t="n">
         <v>2.3</v>
       </c>
-      <c r="G15" s="6" t="n">
+      <c r="G15" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="H15" s="6" t="n">
+      <c r="H15" s="5" t="n">
         <v>2.1</v>
       </c>
-      <c r="I15" s="6" t="n">
+      <c r="I15" s="5" t="n">
         <v>2.6</v>
       </c>
-      <c r="J15" s="6" t="n">
+      <c r="J15" s="5" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="n">
+      <c r="A16" s="3" t="n">
         <v>43160</v>
       </c>
-      <c r="B16" s="5" t="n">
+      <c r="B16" s="4" t="n">
         <v>2.03430483464496</v>
       </c>
-      <c r="C16" s="5" t="n">
+      <c r="C16" s="4" t="n">
         <v>1.99471464090839</v>
       </c>
-      <c r="D16" s="6" t="n">
+      <c r="D16" s="5" t="n">
         <v>2.3</v>
       </c>
-      <c r="E16" s="6" t="n">
+      <c r="E16" s="5" t="n">
         <v>2.5</v>
       </c>
-      <c r="F16" s="6" t="n">
+      <c r="F16" s="5" t="n">
         <v>1.9</v>
       </c>
-      <c r="G16" s="6" t="n">
+      <c r="G16" s="5" t="n">
         <v>3.1</v>
       </c>
-      <c r="H16" s="6" t="n">
+      <c r="H16" s="5" t="n">
         <v>2.4</v>
       </c>
-      <c r="I16" s="6" t="n">
+      <c r="I16" s="5" t="n">
         <v>2.1</v>
       </c>
-      <c r="J16" s="6" t="n">
+      <c r="J16" s="5" t="n">
         <v>3.1</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="n">
+      <c r="A17" s="3" t="n">
         <v>43191</v>
       </c>
-      <c r="B17" s="5" t="n">
+      <c r="B17" s="4" t="n">
         <v>1.17188841132135</v>
       </c>
-      <c r="C17" s="5" t="n">
+      <c r="C17" s="4" t="n">
         <v>1.1494379425735</v>
       </c>
-      <c r="D17" s="6" t="n">
+      <c r="D17" s="5" t="n">
         <v>2.7</v>
       </c>
-      <c r="E17" s="6" t="n">
+      <c r="E17" s="5" t="n">
         <v>2.6</v>
       </c>
-      <c r="F17" s="6" t="n">
+      <c r="F17" s="5" t="n">
         <v>2.9</v>
       </c>
-      <c r="G17" s="6" t="n">
+      <c r="G17" s="5" t="n">
         <v>2.8</v>
       </c>
-      <c r="H17" s="6" t="n">
+      <c r="H17" s="5" t="n">
         <v>2.6</v>
       </c>
-      <c r="I17" s="6" t="n">
+      <c r="I17" s="5" t="n">
         <v>3.4</v>
       </c>
-      <c r="J17" s="6" t="n">
+      <c r="J17" s="5" t="n">
         <v>2.7</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="n">
+      <c r="A18" s="3" t="n">
         <v>43221</v>
       </c>
-      <c r="B18" s="5" t="n">
+      <c r="B18" s="4" t="n">
         <v>20.0361733351689</v>
       </c>
-      <c r="C18" s="5" t="n">
+      <c r="C18" s="4" t="n">
         <v>21.2419587951234</v>
       </c>
-      <c r="D18" s="6" t="n">
+      <c r="D18" s="5" t="n">
         <v>2.1</v>
       </c>
-      <c r="E18" s="6" t="n">
+      <c r="E18" s="5" t="n">
         <v>1.9</v>
       </c>
-      <c r="F18" s="6" t="n">
+      <c r="F18" s="5" t="n">
         <v>2.2</v>
       </c>
-      <c r="G18" s="6" t="n">
+      <c r="G18" s="5" t="n">
         <v>2.3</v>
       </c>
-      <c r="H18" s="6" t="n">
+      <c r="H18" s="5" t="n">
         <v>2.6</v>
       </c>
-      <c r="I18" s="6" t="n">
+      <c r="I18" s="5" t="n">
         <v>1.8</v>
       </c>
-      <c r="J18" s="6" t="n">
+      <c r="J18" s="5" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="n">
+      <c r="A19" s="3" t="n">
         <v>43252</v>
       </c>
-      <c r="B19" s="5" t="n">
+      <c r="B19" s="4" t="n">
         <v>12.0736336019936</v>
       </c>
-      <c r="C19" s="5" t="n">
+      <c r="C19" s="4" t="n">
         <v>12.4052648669979</v>
       </c>
-      <c r="D19" s="6" t="n">
+      <c r="D19" s="5" t="n">
         <v>3.7</v>
       </c>
-      <c r="E19" s="6" t="n">
+      <c r="E19" s="5" t="n">
         <v>3.9</v>
       </c>
-      <c r="F19" s="6" t="n">
+      <c r="F19" s="5" t="n">
         <v>3.7</v>
       </c>
-      <c r="G19" s="6" t="n">
+      <c r="G19" s="5" t="n">
         <v>3.4</v>
       </c>
-      <c r="H19" s="6" t="n">
+      <c r="H19" s="5" t="n">
         <v>3.1</v>
       </c>
-      <c r="I19" s="6" t="n">
+      <c r="I19" s="5" t="n">
         <v>3.6</v>
       </c>
-      <c r="J19" s="6" t="n">
+      <c r="J19" s="5" t="n">
         <v>3.3</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="4" t="n">
+      <c r="A20" s="3" t="n">
         <v>43282</v>
       </c>
-      <c r="B20" s="5" t="n">
+      <c r="B20" s="4" t="n">
         <v>-3.40229772116207</v>
       </c>
-      <c r="C20" s="5" t="n">
+      <c r="C20" s="4" t="n">
         <v>-3.2846513772296</v>
       </c>
-      <c r="D20" s="6" t="n">
+      <c r="D20" s="5" t="n">
         <v>3.1</v>
       </c>
-      <c r="E20" s="6" t="n">
+      <c r="E20" s="5" t="n">
         <v>2.8</v>
       </c>
-      <c r="F20" s="6" t="n">
+      <c r="F20" s="5" t="n">
         <v>3.3</v>
       </c>
-      <c r="G20" s="6" t="n">
+      <c r="G20" s="5" t="n">
         <v>3.4</v>
       </c>
-      <c r="H20" s="6" t="n">
+      <c r="H20" s="5" t="n">
         <v>3.4</v>
       </c>
-      <c r="I20" s="6" t="n">
+      <c r="I20" s="5" t="n">
         <v>3.6</v>
       </c>
-      <c r="J20" s="6" t="n">
+      <c r="J20" s="5" t="n">
         <v>3.2</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4" t="n">
+      <c r="A21" s="3" t="n">
         <v>43313</v>
       </c>
-      <c r="B21" s="5" t="n">
+      <c r="B21" s="4" t="n">
         <v>27.115277050057</v>
       </c>
-      <c r="C21" s="5" t="n">
+      <c r="C21" s="4" t="n">
         <v>28.9437999154046</v>
       </c>
-      <c r="D21" s="6" t="n">
+      <c r="D21" s="5" t="n">
         <v>3.9</v>
       </c>
-      <c r="E21" s="6" t="n">
+      <c r="E21" s="5" t="n">
         <v>4.1</v>
       </c>
-      <c r="F21" s="6" t="n">
+      <c r="F21" s="5" t="n">
         <v>3.7</v>
       </c>
-      <c r="G21" s="6" t="n">
+      <c r="G21" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="H21" s="6" t="n">
+      <c r="H21" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="I21" s="6" t="n">
+      <c r="I21" s="5" t="n">
         <v>3.4</v>
       </c>
-      <c r="J21" s="6" t="n">
+      <c r="J21" s="5" t="n">
         <v>3.6</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="4" t="n">
+      <c r="A22" s="3" t="n">
         <v>43344</v>
       </c>
-      <c r="B22" s="5" t="n">
+      <c r="B22" s="4" t="n">
         <v>8.77055804191055</v>
       </c>
-      <c r="C22" s="5" t="n">
+      <c r="C22" s="4" t="n">
         <v>8.32763402406012</v>
       </c>
-      <c r="D22" s="6" t="n">
+      <c r="D22" s="5" t="n">
         <v>6.5</v>
       </c>
-      <c r="E22" s="6" t="n">
+      <c r="E22" s="5" t="n">
         <v>6.6</v>
       </c>
-      <c r="F22" s="6" t="n">
+      <c r="F22" s="5" t="n">
         <v>6.3</v>
       </c>
-      <c r="G22" s="6" t="n">
+      <c r="G22" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="H22" s="6" t="n">
+      <c r="H22" s="5" t="n">
         <v>7.3</v>
       </c>
-      <c r="I22" s="6" t="n">
+      <c r="I22" s="5" t="n">
         <v>6.8</v>
       </c>
-      <c r="J22" s="6" t="n">
+      <c r="J22" s="5" t="n">
         <v>6.6</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="4" t="n">
+      <c r="A23" s="3" t="n">
         <v>43374</v>
       </c>
-      <c r="B23" s="5" t="n">
+      <c r="B23" s="4" t="n">
         <v>-13.0265194837901</v>
       </c>
-      <c r="C23" s="5" t="n">
+      <c r="C23" s="4" t="n">
         <v>-12.3550239378541</v>
       </c>
-      <c r="D23" s="6" t="n">
+      <c r="D23" s="5" t="n">
         <v>5.4</v>
       </c>
-      <c r="E23" s="6" t="n">
+      <c r="E23" s="5" t="n">
         <v>5.1</v>
       </c>
-      <c r="F23" s="6" t="n">
+      <c r="F23" s="5" t="n">
         <v>5.8</v>
       </c>
-      <c r="G23" s="6" t="n">
+      <c r="G23" s="5" t="n">
         <v>5.3</v>
       </c>
-      <c r="H23" s="6" t="n">
+      <c r="H23" s="5" t="n">
         <v>4.9</v>
       </c>
-      <c r="I23" s="6" t="n">
+      <c r="I23" s="5" t="n">
         <v>5.9</v>
       </c>
-      <c r="J23" s="6" t="n">
+      <c r="J23" s="5" t="n">
         <v>5.8</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="4" t="n">
+      <c r="A24" s="3" t="n">
         <v>43405</v>
       </c>
-      <c r="B24" s="5" t="n">
+      <c r="B24" s="4" t="n">
         <v>4.25596144187959</v>
       </c>
-      <c r="C24" s="5" t="n">
+      <c r="C24" s="4" t="n">
         <v>4.02738991379399</v>
       </c>
-      <c r="D24" s="6" t="n">
+      <c r="D24" s="5" t="n">
         <v>3.2</v>
       </c>
-      <c r="E24" s="6" t="n">
+      <c r="E24" s="5" t="n">
         <v>2.9</v>
       </c>
-      <c r="F24" s="6" t="n">
+      <c r="F24" s="5" t="n">
         <v>3.3</v>
       </c>
-      <c r="G24" s="6" t="n">
+      <c r="G24" s="5" t="n">
         <v>3.3</v>
       </c>
-      <c r="H24" s="6" t="n">
+      <c r="H24" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="I24" s="6" t="n">
+      <c r="I24" s="5" t="n">
         <v>3.7</v>
       </c>
-      <c r="J24" s="6" t="n">
+      <c r="J24" s="5" t="n">
         <v>4.2</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="4" t="n">
+      <c r="A25" s="3" t="n">
         <v>43435</v>
       </c>
-      <c r="B25" s="5" t="n">
+      <c r="B25" s="4" t="n">
         <v>6.71393028376285</v>
       </c>
-      <c r="C25" s="5" t="n">
+      <c r="C25" s="4" t="n">
         <v>6.37158143861078</v>
       </c>
-      <c r="D25" s="6" t="n">
+      <c r="D25" s="5" t="n">
         <v>2.6</v>
       </c>
-      <c r="E25" s="6" t="n">
+      <c r="E25" s="5" t="n">
         <v>2.8</v>
       </c>
-      <c r="F25" s="6" t="n">
+      <c r="F25" s="5" t="n">
         <v>2.3</v>
       </c>
-      <c r="G25" s="6" t="n">
+      <c r="G25" s="5" t="n">
         <v>2.3</v>
       </c>
-      <c r="H25" s="6" t="n">
+      <c r="H25" s="5" t="n">
         <v>2.5</v>
       </c>
-      <c r="I25" s="6" t="n">
+      <c r="I25" s="5" t="n">
         <v>2.5</v>
       </c>
-      <c r="J25" s="6" t="n">
+      <c r="J25" s="5" t="n">
         <v>2.6</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="4" t="n">
+      <c r="A26" s="3" t="n">
         <v>43466</v>
       </c>
-      <c r="B26" s="5" t="n">
+      <c r="B26" s="4" t="n">
         <v>-8.11255448123685</v>
       </c>
-      <c r="C26" s="5" t="n">
+      <c r="C26" s="4" t="n">
         <v>-7.69610411361283</v>
       </c>
-      <c r="D26" s="6" t="n">
+      <c r="D26" s="5" t="n">
         <v>2.9</v>
       </c>
-      <c r="E26" s="6" t="n">
+      <c r="E26" s="5" t="n">
         <v>2.8</v>
       </c>
-      <c r="F26" s="6" t="n">
+      <c r="F26" s="5" t="n">
         <v>2.9</v>
       </c>
-      <c r="G26" s="6" t="n">
+      <c r="G26" s="5" t="n">
         <v>3.2</v>
       </c>
-      <c r="H26" s="6" t="n">
+      <c r="H26" s="5" t="n">
         <v>3.4</v>
       </c>
-      <c r="I26" s="6" t="n">
+      <c r="I26" s="5" t="n">
         <v>2.9</v>
       </c>
-      <c r="J26" s="6" t="n">
+      <c r="J26" s="5" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="4" t="n">
+      <c r="A27" s="3" t="n">
         <v>43497</v>
       </c>
-      <c r="B27" s="5" t="n">
+      <c r="B27" s="4" t="n">
         <v>6.80534632450156</v>
       </c>
-      <c r="C27" s="5" t="n">
+      <c r="C27" s="4" t="n">
         <v>3.92207131532813</v>
       </c>
-      <c r="D27" s="6" t="n">
+      <c r="D27" s="5" t="n">
         <v>3.8</v>
       </c>
-      <c r="E27" s="6" t="n">
+      <c r="E27" s="5" t="n">
         <v>3.8</v>
       </c>
-      <c r="F27" s="6" t="n">
+      <c r="F27" s="5" t="n">
         <v>3.6</v>
       </c>
-      <c r="G27" s="6" t="n">
+      <c r="G27" s="5" t="n">
         <v>4.2</v>
       </c>
-      <c r="H27" s="6" t="n">
+      <c r="H27" s="5" t="n">
         <v>4.5</v>
       </c>
-      <c r="I27" s="6" t="n">
+      <c r="I27" s="5" t="n">
         <v>3.8</v>
       </c>
-      <c r="J27" s="6" t="n">
+      <c r="J27" s="5" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="4" t="n">
+      <c r="A28" s="3" t="n">
         <v>43525</v>
       </c>
-      <c r="B28" s="5" t="n">
+      <c r="B28" s="4" t="n">
         <v>11.5441114211302</v>
       </c>
-      <c r="C28" s="5" t="n">
+      <c r="C28" s="4" t="n">
         <v>11.2641636155965</v>
       </c>
-      <c r="D28" s="6" t="n">
+      <c r="D28" s="5" t="n">
         <v>4.7</v>
       </c>
-      <c r="E28" s="6" t="n">
+      <c r="E28" s="5" t="n">
         <v>4.8</v>
       </c>
-      <c r="F28" s="6" t="n">
+      <c r="F28" s="5" t="n">
         <v>4.5</v>
       </c>
-      <c r="G28" s="6" t="n">
+      <c r="G28" s="5" t="n">
         <v>4.9</v>
       </c>
-      <c r="H28" s="6" t="n">
+      <c r="H28" s="5" t="n">
         <v>5.1</v>
       </c>
-      <c r="I28" s="6" t="n">
+      <c r="I28" s="5" t="n">
         <v>4.4</v>
       </c>
-      <c r="J28" s="6" t="n">
+      <c r="J28" s="5" t="n">
         <v>4.3</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="4" t="n">
+      <c r="A29" s="3" t="n">
         <v>43556</v>
       </c>
-      <c r="B29" s="5" t="n">
+      <c r="B29" s="4" t="n">
         <v>5.36352158326318</v>
       </c>
-      <c r="C29" s="5" t="n">
+      <c r="C29" s="4" t="n">
         <v>5.24381142034838</v>
       </c>
-      <c r="D29" s="6" t="n">
+      <c r="D29" s="5" t="n">
         <v>3.4</v>
       </c>
-      <c r="E29" s="6" t="n">
+      <c r="E29" s="5" t="n">
         <v>3.2</v>
       </c>
-      <c r="F29" s="6" t="n">
+      <c r="F29" s="5" t="n">
         <v>3.7</v>
       </c>
-      <c r="G29" s="6" t="n">
+      <c r="G29" s="5" t="n">
         <v>3.6</v>
       </c>
-      <c r="H29" s="6" t="n">
+      <c r="H29" s="5" t="n">
         <v>3.5</v>
       </c>
-      <c r="I29" s="6" t="n">
+      <c r="I29" s="5" t="n">
         <v>3.3</v>
       </c>
-      <c r="J29" s="6" t="n">
+      <c r="J29" s="5" t="n">
         <v>3.5</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="4" t="n">
+      <c r="A30" s="3" t="n">
         <v>43586</v>
       </c>
-      <c r="B30" s="5" t="n">
+      <c r="B30" s="4" t="n">
         <v>-1.11733005981252</v>
       </c>
-      <c r="C30" s="5" t="n">
+      <c r="C30" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="D30" s="6" t="n">
+      <c r="D30" s="5" t="n">
         <v>3.1</v>
       </c>
-      <c r="E30" s="6" t="n">
+      <c r="E30" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="F30" s="6" t="n">
+      <c r="F30" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="G30" s="6" t="n">
+      <c r="G30" s="5" t="n">
         <v>3.9</v>
       </c>
-      <c r="H30" s="6" t="n">
+      <c r="H30" s="5" t="n">
         <v>2.8</v>
       </c>
-      <c r="I30" s="6" t="n">
+      <c r="I30" s="5" t="n">
         <v>2.9</v>
       </c>
-      <c r="J30" s="6" t="n">
+      <c r="J30" s="5" t="n">
         <v>3.4</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="4" t="n">
+      <c r="A31" s="3" t="n">
         <v>43617</v>
       </c>
-      <c r="B31" s="5" t="n">
+      <c r="B31" s="4" t="n">
         <v>-5.07021031199623</v>
       </c>
-      <c r="C31" s="5" t="n">
+      <c r="C31" s="4" t="n">
         <v>-4.90075791066946</v>
       </c>
-      <c r="D31" s="6" t="n">
+      <c r="D31" s="5" t="n">
         <v>2.7</v>
       </c>
-      <c r="E31" s="6" t="n">
+      <c r="E31" s="5" t="n">
         <v>2.6</v>
       </c>
-      <c r="F31" s="6" t="n">
+      <c r="F31" s="5" t="n">
         <v>2.8</v>
       </c>
-      <c r="G31" s="6" t="n">
+      <c r="G31" s="5" t="n">
         <v>2.8</v>
       </c>
-      <c r="H31" s="6" t="n">
+      <c r="H31" s="5" t="n">
         <v>2.9</v>
       </c>
-      <c r="I31" s="6" t="n">
+      <c r="I31" s="5" t="n">
         <v>2.6</v>
       </c>
-      <c r="J31" s="6" t="n">
+      <c r="J31" s="5" t="n">
         <v>2.8</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="4" t="n">
+      <c r="A32" s="3" t="n">
         <v>43647</v>
       </c>
-      <c r="B32" s="5" t="n">
+      <c r="B32" s="4" t="n">
         <v>3.25610160493122</v>
       </c>
-      <c r="C32" s="5" t="n">
+      <c r="C32" s="4" t="n">
         <v>3.14632694557851</v>
       </c>
-      <c r="D32" s="6" t="n">
+      <c r="D32" s="5" t="n">
         <v>2.2</v>
       </c>
-      <c r="E32" s="6" t="n">
+      <c r="E32" s="5" t="n">
         <v>2.1</v>
       </c>
-      <c r="F32" s="6" t="n">
+      <c r="F32" s="5" t="n">
         <v>2.2</v>
       </c>
-      <c r="G32" s="6" t="n">
+      <c r="G32" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="H32" s="6" t="n">
+      <c r="H32" s="5" t="n">
         <v>1.9</v>
       </c>
-      <c r="I32" s="6" t="n">
+      <c r="I32" s="5" t="n">
         <v>2.8</v>
       </c>
-      <c r="J32" s="6" t="n">
+      <c r="J32" s="5" t="n">
         <v>2.5</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="4" t="n">
+      <c r="A33" s="3" t="n">
         <v>43678</v>
       </c>
-      <c r="B33" s="5" t="n">
+      <c r="B33" s="4" t="n">
         <v>31.6996460120556</v>
       </c>
-      <c r="C33" s="5" t="n">
+      <c r="C33" s="4" t="n">
         <v>33.2037639553347</v>
       </c>
-      <c r="D33" s="6" t="n">
+      <c r="D33" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="E33" s="6" t="n">
+      <c r="E33" s="5" t="n">
         <v>3.9</v>
       </c>
-      <c r="F33" s="6" t="n">
+      <c r="F33" s="5" t="n">
         <v>3.9</v>
       </c>
-      <c r="G33" s="6" t="n">
+      <c r="G33" s="5" t="n">
         <v>4.1</v>
       </c>
-      <c r="H33" s="6" t="n">
+      <c r="H33" s="5" t="n">
         <v>4.5</v>
       </c>
-      <c r="I33" s="6" t="n">
+      <c r="I33" s="5" t="n">
         <v>4.4</v>
       </c>
-      <c r="J33" s="6" t="n">
+      <c r="J33" s="5" t="n">
         <v>4.2</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="4" t="n">
+      <c r="A34" s="3" t="n">
         <v>43709</v>
       </c>
-      <c r="B34" s="5" t="n">
+      <c r="B34" s="4" t="n">
         <v>-2.96004697762907</v>
       </c>
-      <c r="C34" s="5" t="n">
+      <c r="C34" s="4" t="n">
         <v>-2.81708769666963</v>
       </c>
-      <c r="D34" s="6" t="n">
+      <c r="D34" s="5" t="n">
         <v>5.9</v>
       </c>
-      <c r="E34" s="6" t="n">
+      <c r="E34" s="5" t="n">
         <v>5.8</v>
       </c>
-      <c r="F34" s="6" t="n">
+      <c r="F34" s="5" t="n">
         <v>6.1</v>
       </c>
-      <c r="G34" s="6" t="n">
+      <c r="G34" s="5" t="n">
         <v>5.8</v>
       </c>
-      <c r="H34" s="6" t="n">
+      <c r="H34" s="5" t="n">
         <v>6.2</v>
       </c>
-      <c r="I34" s="6" t="n">
+      <c r="I34" s="5" t="n">
         <v>5.8</v>
       </c>
-      <c r="J34" s="6" t="n">
+      <c r="J34" s="5" t="n">
         <v>5.3</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="4" t="n">
+      <c r="A35" s="3" t="n">
         <v>43739</v>
       </c>
-      <c r="B35" s="5" t="n">
+      <c r="B35" s="4" t="n">
         <v>12.4910649580616</v>
       </c>
-      <c r="C35" s="5" t="n">
+      <c r="C35" s="4" t="n">
         <v>11.9142655172423</v>
       </c>
-      <c r="D35" s="6" t="n">
+      <c r="D35" s="5" t="n">
         <v>3.3</v>
       </c>
-      <c r="E35" s="6" t="n">
+      <c r="E35" s="5" t="n">
         <v>3.2</v>
       </c>
-      <c r="F35" s="6" t="n">
+      <c r="F35" s="5" t="n">
         <v>3.4</v>
       </c>
-      <c r="G35" s="6" t="n">
+      <c r="G35" s="5" t="n">
         <v>2.9</v>
       </c>
-      <c r="H35" s="6" t="n">
+      <c r="H35" s="5" t="n">
         <v>3.3</v>
       </c>
-      <c r="I35" s="6" t="n">
+      <c r="I35" s="5" t="n">
         <v>3.7</v>
       </c>
-      <c r="J35" s="6" t="n">
+      <c r="J35" s="5" t="n">
         <v>3.2</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="4" t="n">
+      <c r="A36" s="3" t="n">
         <v>43770</v>
       </c>
-      <c r="B36" s="5" t="n">
+      <c r="B36" s="4" t="n">
         <v>0.378072283990615</v>
       </c>
-      <c r="C36" s="5" t="n">
+      <c r="C36" s="4" t="n">
         <v>0.361664047018851</v>
       </c>
-      <c r="D36" s="6" t="n">
+      <c r="D36" s="5" t="n">
         <v>4.3</v>
       </c>
-      <c r="E36" s="6" t="n">
+      <c r="E36" s="5" t="n">
         <v>4.1</v>
       </c>
-      <c r="F36" s="6" t="n">
+      <c r="F36" s="5" t="n">
         <v>4.5</v>
       </c>
-      <c r="G36" s="6" t="n">
+      <c r="G36" s="5" t="n">
         <v>3.9</v>
       </c>
-      <c r="H36" s="6" t="n">
+      <c r="H36" s="5" t="n">
         <v>4.3</v>
       </c>
-      <c r="I36" s="6" t="n">
+      <c r="I36" s="5" t="n">
         <v>4.5</v>
       </c>
-      <c r="J36" s="6" t="n">
+      <c r="J36" s="5" t="n">
         <v>4.5</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="4" t="n">
+      <c r="A37" s="3" t="n">
         <v>43800</v>
       </c>
-      <c r="B37" s="5" t="n">
+      <c r="B37" s="4" t="n">
         <v>10.3849941352459</v>
       </c>
-      <c r="C37" s="5" t="n">
+      <c r="C37" s="4" t="n">
         <v>12.5375479720915</v>
       </c>
-      <c r="D37" s="6" t="n">
+      <c r="D37" s="5" t="n">
         <v>3.7</v>
       </c>
-      <c r="E37" s="6" t="n">
+      <c r="E37" s="5" t="n">
         <v>3.8</v>
       </c>
-      <c r="F37" s="6" t="n">
+      <c r="F37" s="5" t="n">
         <v>3.6</v>
       </c>
-      <c r="G37" s="6" t="n">
+      <c r="G37" s="5" t="n">
         <v>3.7</v>
       </c>
-      <c r="H37" s="6" t="n">
+      <c r="H37" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="I37" s="6" t="n">
+      <c r="I37" s="5" t="n">
         <v>3.3</v>
       </c>
-      <c r="J37" s="6" t="n">
+      <c r="J37" s="5" t="n">
         <v>4.2</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="4" t="n">
+      <c r="A38" s="3" t="n">
         <v>43831</v>
       </c>
-      <c r="B38" s="5" t="n">
+      <c r="B38" s="4" t="n">
         <v>0.677968698537877</v>
       </c>
-      <c r="C38" s="5" t="n">
+      <c r="C38" s="4" t="n">
         <v>-0.638979809877101</v>
       </c>
-      <c r="D38" s="6" t="n">
+      <c r="D38" s="5" t="n">
         <v>2.3</v>
       </c>
-      <c r="E38" s="6" t="n">
+      <c r="E38" s="5" t="n">
         <v>1.9</v>
       </c>
-      <c r="F38" s="6" t="n">
+      <c r="F38" s="5" t="n">
         <v>2.5</v>
       </c>
-      <c r="G38" s="6" t="n">
+      <c r="G38" s="5" t="n">
         <v>2.4</v>
       </c>
-      <c r="H38" s="6" t="n">
+      <c r="H38" s="5" t="n">
         <v>3.1</v>
       </c>
-      <c r="I38" s="6" t="n">
+      <c r="I38" s="5" t="n">
         <v>2.5</v>
       </c>
-      <c r="J38" s="6" t="n">
+      <c r="J38" s="5" t="n">
         <v>2.5</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="4" t="n">
+      <c r="A39" s="3" t="n">
         <v>43862</v>
       </c>
-      <c r="B39" s="5" t="n">
+      <c r="B39" s="4" t="n">
         <v>0.673403218134412</v>
       </c>
-      <c r="C39" s="5" t="n">
+      <c r="C39" s="4" t="n">
         <v>0.638979809877099</v>
       </c>
-      <c r="D39" s="6" t="n">
+      <c r="D39" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E39" s="6" t="n">
+      <c r="E39" s="5" t="n">
         <v>1.8</v>
       </c>
-      <c r="F39" s="6" t="n">
+      <c r="F39" s="5" t="n">
         <v>2.3</v>
       </c>
-      <c r="G39" s="6" t="n">
+      <c r="G39" s="5" t="n">
         <v>1.8</v>
       </c>
-      <c r="H39" s="6" t="n">
+      <c r="H39" s="5" t="n">
         <v>2.2</v>
       </c>
-      <c r="I39" s="6" t="n">
+      <c r="I39" s="5" t="n">
         <v>2.3</v>
       </c>
-      <c r="J39" s="6" t="n">
+      <c r="J39" s="5" t="n">
         <v>1.8</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="4" t="n">
+      <c r="A40" s="3" t="n">
         <v>43891</v>
       </c>
-      <c r="B40" s="5" t="n">
+      <c r="B40" s="4" t="n">
         <v>5.22994994028488</v>
       </c>
-      <c r="C40" s="5" t="n">
+      <c r="C40" s="4" t="n">
         <v>6.1748007068447</v>
       </c>
-      <c r="D40" s="6" t="n">
+      <c r="D40" s="5" t="n">
         <v>3.3</v>
       </c>
-      <c r="E40" s="6" t="n">
+      <c r="E40" s="5" t="n">
         <v>3.6</v>
       </c>
-      <c r="F40" s="6" t="n">
+      <c r="F40" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="G40" s="6" t="n">
+      <c r="G40" s="5" t="n">
         <v>3.8</v>
       </c>
-      <c r="H40" s="6" t="n">
+      <c r="H40" s="5" t="n">
         <v>3.5</v>
       </c>
-      <c r="I40" s="6" t="n">
+      <c r="I40" s="5" t="n">
         <v>3.1</v>
       </c>
-      <c r="J40" s="6" t="n">
+      <c r="J40" s="5" t="n">
         <v>2.6</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="4" t="n">
+      <c r="A41" s="3" t="n">
         <v>43922</v>
       </c>
-      <c r="B41" s="5" t="n">
+      <c r="B41" s="4" t="n">
         <v>31.9032602335857</v>
       </c>
-      <c r="C41" s="5" t="n">
+      <c r="C41" s="4" t="n">
         <v>34.5837992608855</v>
       </c>
-      <c r="D41" s="6" t="n">
+      <c r="D41" s="5" t="n">
         <v>1.5</v>
       </c>
-      <c r="E41" s="6" t="n">
+      <c r="E41" s="5" t="n">
         <v>1.4</v>
       </c>
-      <c r="F41" s="6" t="n">
+      <c r="F41" s="5" t="n">
         <v>1.5</v>
       </c>
-      <c r="G41" s="6" t="n">
+      <c r="G41" s="5" t="n">
         <v>2.6</v>
       </c>
-      <c r="H41" s="6" t="n">
+      <c r="H41" s="5" t="n">
         <v>2.1</v>
       </c>
-      <c r="I41" s="6" t="n">
+      <c r="I41" s="5" t="n">
         <v>1.3</v>
       </c>
-      <c r="J41" s="6" t="n">
+      <c r="J41" s="5" t="n">
         <v>0.6</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="4" t="n">
+      <c r="A42" s="3" t="n">
         <v>43952</v>
       </c>
-      <c r="B42" s="5" t="n">
+      <c r="B42" s="4" t="n">
         <v>6.28009012390304</v>
       </c>
-      <c r="C42" s="5" t="n">
+      <c r="C42" s="4" t="n">
         <v>5.76291128366364</v>
       </c>
-      <c r="D42" s="6" t="n">
+      <c r="D42" s="5" t="n">
         <v>1.5</v>
       </c>
-      <c r="E42" s="6" t="n">
+      <c r="E42" s="5" t="n">
         <v>1.5</v>
       </c>
-      <c r="F42" s="6" t="n">
+      <c r="F42" s="5" t="n">
         <v>1.6</v>
       </c>
-      <c r="G42" s="6" t="n">
+      <c r="G42" s="5" t="n">
         <v>1.7</v>
       </c>
-      <c r="H42" s="6" t="n">
+      <c r="H42" s="5" t="n">
         <v>1.6</v>
       </c>
-      <c r="I42" s="6" t="n">
+      <c r="I42" s="5" t="n">
         <v>1.3</v>
       </c>
-      <c r="J42" s="6" t="n">
+      <c r="J42" s="5" t="n">
         <v>1.6</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="4" t="n">
+      <c r="A43" s="3" t="n">
         <v>43983</v>
       </c>
-      <c r="B43" s="5" t="n">
+      <c r="B43" s="4" t="n">
         <v>0.865806274311453</v>
       </c>
-      <c r="C43" s="5" t="n">
+      <c r="C43" s="4" t="n">
         <v>0.796816964917688</v>
       </c>
-      <c r="D43" s="6" t="n">
+      <c r="D43" s="5" t="n">
         <v>2.2</v>
       </c>
-      <c r="E43" s="6" t="n">
+      <c r="E43" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F43" s="6" t="n">
+      <c r="F43" s="5" t="n">
         <v>2.5</v>
       </c>
-      <c r="G43" s="6" t="n">
+      <c r="G43" s="5" t="n">
         <v>2.2</v>
       </c>
-      <c r="H43" s="6" t="n">
+      <c r="H43" s="5" t="n">
         <v>2.3</v>
       </c>
-      <c r="I43" s="6" t="n">
+      <c r="I43" s="5" t="n">
         <v>2.3</v>
       </c>
-      <c r="J43" s="6" t="n">
+      <c r="J43" s="5" t="n">
         <v>1.9</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="4" t="n">
+      <c r="A44" s="3" t="n">
         <v>44013</v>
       </c>
-      <c r="B44" s="5" t="n">
+      <c r="B44" s="4" t="n">
         <v>12.1607132094787</v>
       </c>
-      <c r="C44" s="5" t="n">
+      <c r="C44" s="4" t="n">
         <v>7.6372978784574</v>
       </c>
-      <c r="D44" s="6" t="n">
+      <c r="D44" s="5" t="n">
         <v>1.9</v>
       </c>
-      <c r="E44" s="6" t="n">
+      <c r="E44" s="5" t="n">
         <v>1.6</v>
       </c>
-      <c r="F44" s="6" t="n">
+      <c r="F44" s="5" t="n">
         <v>2.1</v>
       </c>
-      <c r="G44" s="6" t="n">
+      <c r="G44" s="5" t="n">
         <v>1.9</v>
       </c>
-      <c r="H44" s="6" t="n">
+      <c r="H44" s="5" t="n">
         <v>2.2</v>
       </c>
-      <c r="I44" s="6" t="n">
+      <c r="I44" s="5" t="n">
         <v>2.3</v>
       </c>
-      <c r="J44" s="6" t="n">
+      <c r="J44" s="5" t="n">
         <v>2.7</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="4" t="n">
+      <c r="A45" s="3" t="n">
         <v>44044</v>
       </c>
-      <c r="B45" s="5" t="n">
+      <c r="B45" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="C45" s="5" t="n">
+      <c r="C45" s="4" t="n">
         <v>-0.738010729762253</v>
       </c>
-      <c r="D45" s="6" t="n">
+      <c r="D45" s="5" t="n">
         <v>2.7</v>
       </c>
-      <c r="E45" s="6" t="n">
+      <c r="E45" s="5" t="n">
         <v>2.8</v>
       </c>
-      <c r="F45" s="6" t="n">
+      <c r="F45" s="5" t="n">
         <v>2.6</v>
       </c>
-      <c r="G45" s="6" t="n">
+      <c r="G45" s="5" t="n">
         <v>2.6</v>
       </c>
-      <c r="H45" s="6" t="n">
+      <c r="H45" s="5" t="n">
         <v>2.3</v>
       </c>
-      <c r="I45" s="6" t="n">
+      <c r="I45" s="5" t="n">
         <v>2.7</v>
       </c>
-      <c r="J45" s="6" t="n">
+      <c r="J45" s="5" t="n">
         <v>2.9</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="4" t="n">
+      <c r="A46" s="3" t="n">
         <v>44075</v>
       </c>
-      <c r="B46" s="5" t="n">
+      <c r="B46" s="4" t="n">
         <v>6.64450994081528</v>
       </c>
-      <c r="C46" s="5" t="n">
+      <c r="C46" s="4" t="n">
         <v>7.8331843269907</v>
       </c>
-      <c r="D46" s="6" t="n">
+      <c r="D46" s="5" t="n">
         <v>2.8</v>
       </c>
-      <c r="E46" s="6" t="n">
+      <c r="E46" s="5" t="n">
         <v>2.8</v>
       </c>
-      <c r="F46" s="6" t="n">
+      <c r="F46" s="5" t="n">
         <v>2.9</v>
       </c>
-      <c r="G46" s="6" t="n">
+      <c r="G46" s="5" t="n">
         <v>2.3</v>
       </c>
-      <c r="H46" s="6" t="n">
+      <c r="H46" s="5" t="n">
         <v>3.4</v>
       </c>
-      <c r="I46" s="6" t="n">
+      <c r="I46" s="5" t="n">
         <v>3.6</v>
       </c>
-      <c r="J46" s="6" t="n">
+      <c r="J46" s="5" t="n">
         <v>2.3</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="4" t="n">
+      <c r="A47" s="3" t="n">
         <v>44105</v>
       </c>
-      <c r="B47" s="5" t="n">
+      <c r="B47" s="4" t="n">
         <v>15.2107778197458</v>
       </c>
-      <c r="C47" s="5" t="n">
+      <c r="C47" s="4" t="n">
         <v>14.6292093214737</v>
       </c>
-      <c r="D47" s="6" t="n">
+      <c r="D47" s="5" t="n">
         <v>3.8</v>
       </c>
-      <c r="E47" s="6" t="n">
+      <c r="E47" s="5" t="n">
         <v>3.6</v>
       </c>
-      <c r="F47" s="6" t="n">
+      <c r="F47" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="G47" s="6" t="n">
+      <c r="G47" s="5" t="n">
         <v>4.1</v>
       </c>
-      <c r="H47" s="6" t="n">
+      <c r="H47" s="5" t="n">
         <v>3.7</v>
       </c>
-      <c r="I47" s="6" t="n">
+      <c r="I47" s="5" t="n">
         <v>3.7</v>
       </c>
-      <c r="J47" s="6" t="n">
+      <c r="J47" s="5" t="n">
         <v>3.5</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="4" t="n">
+      <c r="A48" s="3" t="n">
         <v>44136</v>
       </c>
-      <c r="B48" s="5" t="n">
+      <c r="B48" s="4" t="n">
         <v>-8.98038948613031</v>
       </c>
-      <c r="C48" s="5" t="n">
+      <c r="C48" s="4" t="n">
         <v>-8.64735980038268</v>
       </c>
-      <c r="D48" s="6" t="n">
+      <c r="D48" s="5" t="n">
         <v>3.2</v>
       </c>
-      <c r="E48" s="6" t="n">
+      <c r="E48" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="F48" s="6" t="n">
+      <c r="F48" s="5" t="n">
         <v>3.4</v>
       </c>
-      <c r="G48" s="6" t="n">
+      <c r="G48" s="5" t="n">
         <v>3.1</v>
       </c>
-      <c r="H48" s="6" t="n">
+      <c r="H48" s="5" t="n">
         <v>3.7</v>
       </c>
-      <c r="I48" s="6" t="n">
+      <c r="I48" s="5" t="n">
         <v>3.1</v>
       </c>
-      <c r="J48" s="6" t="n">
+      <c r="J48" s="5" t="n">
         <v>2.9</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="4" t="n">
+      <c r="A49" s="3" t="n">
         <v>44166</v>
       </c>
-      <c r="B49" s="5" t="n">
+      <c r="B49" s="4" t="n">
         <v>7.12275092883678</v>
       </c>
-      <c r="C49" s="5" t="n">
+      <c r="C49" s="4" t="n">
         <v>6.85626714372967</v>
       </c>
-      <c r="D49" s="6" t="n">
+      <c r="D49" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="E49" s="6" t="n">
+      <c r="E49" s="5" t="n">
         <v>3.7</v>
       </c>
-      <c r="F49" s="6" t="n">
+      <c r="F49" s="5" t="n">
         <v>4.2</v>
       </c>
-      <c r="G49" s="6" t="n">
+      <c r="G49" s="5" t="n">
         <v>4.3</v>
       </c>
-      <c r="H49" s="6" t="n">
+      <c r="H49" s="5" t="n">
         <v>5.5</v>
       </c>
-      <c r="I49" s="6" t="n">
+      <c r="I49" s="5" t="n">
         <v>4.3</v>
       </c>
-      <c r="J49" s="6" t="n">
+      <c r="J49" s="5" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="4" t="n">
+      <c r="A50" s="3" t="n">
         <v>44197</v>
       </c>
-      <c r="B50" s="5" t="n">
+      <c r="B50" s="4" t="n">
         <v>-7.79615414697118</v>
       </c>
-      <c r="C50" s="5" t="n">
+      <c r="C50" s="4" t="n">
         <v>-8.15498669641077</v>
       </c>
-      <c r="D50" s="6" t="n">
+      <c r="D50" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="E50" s="6" t="n">
+      <c r="E50" s="5" t="n">
         <v>3.3</v>
       </c>
-      <c r="F50" s="6" t="n">
+      <c r="F50" s="5" t="n">
         <v>4.6</v>
       </c>
-      <c r="G50" s="6" t="n">
+      <c r="G50" s="5" t="n">
         <v>5.5</v>
       </c>
-      <c r="H50" s="6" t="n">
+      <c r="H50" s="5" t="n">
         <v>4.3</v>
       </c>
-      <c r="I50" s="6" t="n">
+      <c r="I50" s="5" t="n">
         <v>4.5</v>
       </c>
-      <c r="J50" s="6" t="n">
+      <c r="J50" s="5" t="n">
         <v>4.1</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="4" t="n">
+      <c r="A51" s="3" t="n">
         <v>44228</v>
       </c>
-      <c r="B51" s="5" t="n">
+      <c r="B51" s="4" t="n">
         <v>-4.84523833859467</v>
       </c>
-      <c r="C51" s="5" t="n">
+      <c r="C51" s="4" t="n">
         <v>-4.6831299684099</v>
       </c>
-      <c r="D51" s="6" t="n">
+      <c r="D51" s="5" t="n">
         <v>3.6</v>
       </c>
-      <c r="E51" s="6" t="n">
+      <c r="E51" s="5" t="n">
         <v>3.6</v>
       </c>
-      <c r="F51" s="6" t="n">
+      <c r="F51" s="5" t="n">
         <v>3.4</v>
       </c>
-      <c r="G51" s="6" t="n">
+      <c r="G51" s="5" t="n">
         <v>3.3</v>
       </c>
-      <c r="H51" s="6" t="n">
+      <c r="H51" s="5" t="n">
         <v>3.8</v>
       </c>
-      <c r="I51" s="6" t="n">
+      <c r="I51" s="5" t="n">
         <v>4.1</v>
       </c>
-      <c r="J51" s="6" t="n">
+      <c r="J51" s="5" t="n">
         <v>3.9</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="4" t="n">
+      <c r="A52" s="3" t="n">
         <v>44256</v>
       </c>
-      <c r="B52" s="5" t="n">
+      <c r="B52" s="4" t="n">
         <v>-3.61050046421163</v>
       </c>
-      <c r="C52" s="5" t="n">
+      <c r="C52" s="4" t="n">
         <v>-3.48467313301682</v>
       </c>
-      <c r="D52" s="6" t="n">
+      <c r="D52" s="5" t="n">
         <v>4.8</v>
       </c>
-      <c r="E52" s="6" t="n">
+      <c r="E52" s="5" t="n">
         <v>5.2</v>
       </c>
-      <c r="F52" s="6" t="n">
+      <c r="F52" s="5" t="n">
         <v>4.8</v>
       </c>
-      <c r="G52" s="6" t="n">
+      <c r="G52" s="5" t="n">
         <v>4.2</v>
       </c>
-      <c r="H52" s="6" t="n">
+      <c r="H52" s="5" t="n">
         <v>3.3</v>
       </c>
-      <c r="I52" s="6" t="n">
+      <c r="I52" s="5" t="n">
         <v>4.3</v>
       </c>
-      <c r="J52" s="6" t="n">
+      <c r="J52" s="5" t="n">
         <v>4.1</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="4" t="n">
+      <c r="A53" s="3" t="n">
         <v>44287</v>
       </c>
-      <c r="B53" s="5" t="n">
+      <c r="B53" s="4" t="n">
         <v>6.40788566845224</v>
       </c>
-      <c r="C53" s="5" t="n">
+      <c r="C53" s="4" t="n">
         <v>6.18754037180875</v>
       </c>
-      <c r="D53" s="6" t="n">
+      <c r="D53" s="5" t="n">
         <v>4.1</v>
       </c>
-      <c r="E53" s="6" t="n">
+      <c r="E53" s="5" t="n">
         <v>4.1</v>
       </c>
-      <c r="F53" s="6" t="n">
+      <c r="F53" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="G53" s="6" t="n">
+      <c r="G53" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="H53" s="6" t="n">
+      <c r="H53" s="5" t="n">
         <v>4.1</v>
       </c>
-      <c r="I53" s="6" t="n">
+      <c r="I53" s="5" t="n">
         <v>4.2</v>
       </c>
-      <c r="J53" s="6" t="n">
+      <c r="J53" s="5" t="n">
         <v>4.8</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="4" t="n">
+      <c r="A54" s="3" t="n">
         <v>44317</v>
       </c>
-      <c r="B54" s="5" t="n">
+      <c r="B54" s="4" t="n">
         <v>4.71467784257021</v>
       </c>
-      <c r="C54" s="5" t="n">
+      <c r="C54" s="4" t="n">
         <v>4.56105112520523</v>
       </c>
-      <c r="D54" s="6" t="n">
+      <c r="D54" s="5" t="n">
         <v>3.3</v>
       </c>
-      <c r="E54" s="6" t="n">
+      <c r="E54" s="5" t="n">
         <v>3.4</v>
       </c>
-      <c r="F54" s="6" t="n">
+      <c r="F54" s="5" t="n">
         <v>3.2</v>
       </c>
-      <c r="G54" s="6" t="n">
+      <c r="G54" s="5" t="n">
         <v>3.2</v>
       </c>
-      <c r="H54" s="6" t="n">
+      <c r="H54" s="5" t="n">
         <v>3.1</v>
       </c>
-      <c r="I54" s="6" t="n">
+      <c r="I54" s="5" t="n">
         <v>3.6</v>
       </c>
-      <c r="J54" s="6" t="n">
+      <c r="J54" s="5" t="n">
         <v>3.5</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="4" t="n">
+      <c r="A55" s="3" t="n">
         <v>44348</v>
       </c>
-      <c r="B55" s="5" t="n">
+      <c r="B55" s="4" t="n">
         <v>6.9869679960486</v>
       </c>
-      <c r="C55" s="5" t="n">
+      <c r="C55" s="4" t="n">
         <v>6.77181740549509</v>
       </c>
-      <c r="D55" s="6" t="n">
+      <c r="D55" s="5" t="n">
         <v>3.2</v>
       </c>
-      <c r="E55" s="6" t="n">
+      <c r="E55" s="5" t="n">
         <v>3.1</v>
       </c>
-      <c r="F55" s="6" t="n">
+      <c r="F55" s="5" t="n">
         <v>3.2</v>
       </c>
-      <c r="G55" s="6" t="n">
+      <c r="G55" s="5" t="n">
         <v>3.3</v>
       </c>
-      <c r="H55" s="6" t="n">
+      <c r="H55" s="5" t="n">
         <v>2.9</v>
       </c>
-      <c r="I55" s="6" t="n">
+      <c r="I55" s="5" t="n">
         <v>3.5</v>
       </c>
-      <c r="J55" s="6" t="n">
+      <c r="J55" s="5" t="n">
         <v>3.4</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="4" t="n">
+      <c r="A56" s="3" t="n">
         <v>44378</v>
       </c>
-      <c r="B56" s="5" t="n">
+      <c r="B56" s="4" t="n">
         <v>7.38888420991582</v>
       </c>
-      <c r="C56" s="5" t="n">
+      <c r="C56" s="4" t="n">
         <v>7.17667983696766</v>
       </c>
-      <c r="D56" s="6" t="n">
+      <c r="D56" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E56" s="6" t="n">
+      <c r="E56" s="5" t="n">
         <v>3.1</v>
       </c>
-      <c r="F56" s="6" t="n">
+      <c r="F56" s="5" t="n">
         <v>2.9</v>
       </c>
-      <c r="G56" s="6" t="n">
+      <c r="G56" s="5" t="n">
         <v>2.8</v>
       </c>
-      <c r="H56" s="6" t="n">
+      <c r="H56" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="I56" s="6" t="n">
+      <c r="I56" s="5" t="n">
         <v>3.2</v>
       </c>
-      <c r="J56" s="6" t="n">
+      <c r="J56" s="5" t="n">
         <v>3.3</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="4" t="n">
+      <c r="A57" s="3" t="n">
         <v>44409</v>
       </c>
-      <c r="B57" s="5" t="n">
+      <c r="B57" s="4" t="n">
         <v>0.568183346743086</v>
       </c>
-      <c r="C57" s="5" t="n">
+      <c r="C57" s="4" t="n">
         <v>0.552487593196981</v>
       </c>
-      <c r="D57" s="6" t="n">
+      <c r="D57" s="5" t="n">
         <v>2.5</v>
       </c>
-      <c r="E57" s="6" t="n">
+      <c r="E57" s="5" t="n">
         <v>2.6</v>
       </c>
-      <c r="F57" s="6" t="n">
+      <c r="F57" s="5" t="n">
         <v>2.3</v>
       </c>
-      <c r="G57" s="6" t="n">
+      <c r="G57" s="5" t="n">
         <v>2.4</v>
       </c>
-      <c r="H57" s="6" t="n">
+      <c r="H57" s="5" t="n">
         <v>2.7</v>
       </c>
-      <c r="I57" s="6" t="n">
+      <c r="I57" s="5" t="n">
         <v>1.8</v>
       </c>
-      <c r="J57" s="6" t="n">
+      <c r="J57" s="5" t="n">
         <v>3.4</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="4" t="n">
+      <c r="A58" s="3" t="n">
         <v>44440</v>
       </c>
-      <c r="B58" s="5" t="n">
+      <c r="B58" s="4" t="n">
         <v>3.06858107034439</v>
       </c>
-      <c r="C58" s="5" t="n">
+      <c r="C58" s="4" t="n">
         <v>2.44910200082957</v>
       </c>
-      <c r="D58" s="6" t="n">
+      <c r="D58" s="5" t="n">
         <v>3.5</v>
       </c>
-      <c r="E58" s="6" t="n">
+      <c r="E58" s="5" t="n">
         <v>3.8</v>
       </c>
-      <c r="F58" s="6" t="n">
+      <c r="F58" s="5" t="n">
         <v>3.4</v>
       </c>
-      <c r="G58" s="6" t="n">
+      <c r="G58" s="5" t="n">
         <v>3.3</v>
       </c>
-      <c r="H58" s="6" t="n">
+      <c r="H58" s="5" t="n">
         <v>2.8</v>
       </c>
-      <c r="I58" s="6" t="n">
+      <c r="I58" s="5" t="n">
         <v>2.9</v>
       </c>
-      <c r="J58" s="6" t="n">
+      <c r="J58" s="5" t="n">
         <v>3.7</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="4" t="n">
+      <c r="A59" s="3" t="n">
         <v>44470</v>
       </c>
-      <c r="B59" s="5" t="n">
+      <c r="B59" s="4" t="n">
         <v>6.12708253930411</v>
       </c>
-      <c r="C59" s="5" t="n">
+      <c r="C59" s="4" t="n">
         <v>5.99919106279753</v>
       </c>
-      <c r="D59" s="6" t="n">
+      <c r="D59" s="5" t="n">
         <v>3.5</v>
       </c>
-      <c r="E59" s="6" t="n">
+      <c r="E59" s="5" t="n">
         <v>3.8</v>
       </c>
-      <c r="F59" s="6" t="n">
+      <c r="F59" s="5" t="n">
         <v>3.4</v>
       </c>
-      <c r="G59" s="6" t="n">
+      <c r="G59" s="5" t="n">
         <v>3.2</v>
       </c>
-      <c r="H59" s="6" t="n">
+      <c r="H59" s="5" t="n">
         <v>3.5</v>
       </c>
-      <c r="I59" s="6" t="n">
+      <c r="I59" s="5" t="n">
         <v>3.1</v>
       </c>
-      <c r="J59" s="6" t="n">
+      <c r="J59" s="5" t="n">
         <v>2.9</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="4" t="n">
+      <c r="A60" s="3" t="n">
         <v>44501</v>
       </c>
-      <c r="B60" s="5" t="n">
+      <c r="B60" s="4" t="n">
         <v>2.046107187134</v>
       </c>
-      <c r="C60" s="5" t="n">
+      <c r="C60" s="4" t="n">
         <v>2.00507970455612</v>
       </c>
-      <c r="D60" s="6" t="n">
+      <c r="D60" s="5" t="n">
         <v>2.5</v>
       </c>
-      <c r="E60" s="6" t="n">
+      <c r="E60" s="5" t="n">
         <v>2.3</v>
       </c>
-      <c r="F60" s="6" t="n">
+      <c r="F60" s="5" t="n">
         <v>2.8</v>
       </c>
-      <c r="G60" s="6" t="n">
+      <c r="G60" s="5" t="n">
         <v>2.7</v>
       </c>
-      <c r="H60" s="6" t="n">
+      <c r="H60" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="I60" s="6" t="n">
+      <c r="I60" s="5" t="n">
         <v>2.7</v>
       </c>
-      <c r="J60" s="6" t="n">
+      <c r="J60" s="5" t="n">
         <v>2.2</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="4" t="n">
+      <c r="A61" s="3" t="n">
         <v>44531</v>
       </c>
-      <c r="B61" s="5" t="n">
+      <c r="B61" s="4" t="n">
         <v>3.23814095030398</v>
       </c>
-      <c r="C61" s="5" t="n">
+      <c r="C61" s="4" t="n">
         <v>3.17486983145803</v>
       </c>
-      <c r="D61" s="6" t="n">
+      <c r="D61" s="5" t="n">
         <v>3.8</v>
       </c>
-      <c r="E61" s="6" t="n">
+      <c r="E61" s="5" t="n">
         <v>4.1</v>
       </c>
-      <c r="F61" s="6" t="n">
+      <c r="F61" s="5" t="n">
         <v>3.5</v>
       </c>
-      <c r="G61" s="6" t="n">
+      <c r="G61" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="H61" s="6" t="n">
+      <c r="H61" s="5" t="n">
         <v>4.4</v>
       </c>
-      <c r="I61" s="6" t="n">
+      <c r="I61" s="5" t="n">
         <v>3.9</v>
       </c>
-      <c r="J61" s="6" t="n">
+      <c r="J61" s="5" t="n">
         <v>3.1</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="4" t="n">
+      <c r="A62" s="3" t="n">
         <v>44562</v>
       </c>
-      <c r="B62" s="5" t="n">
+      <c r="B62" s="4" t="n">
         <v>2.42142581205945</v>
       </c>
-      <c r="C62" s="5" t="n">
+      <c r="C62" s="4" t="n">
         <v>2.37540860081071</v>
       </c>
-      <c r="D62" s="6" t="n">
+      <c r="D62" s="5" t="n">
         <v>3.9</v>
       </c>
-      <c r="E62" s="6" t="n">
+      <c r="E62" s="5" t="n">
         <v>3.9</v>
       </c>
-      <c r="F62" s="6" t="n">
+      <c r="F62" s="5" t="n">
         <v>3.8</v>
       </c>
-      <c r="G62" s="6" t="n">
+      <c r="G62" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="H62" s="6" t="n">
+      <c r="H62" s="5" t="n">
         <v>3.4</v>
       </c>
-      <c r="I62" s="6" t="n">
+      <c r="I62" s="5" t="n">
         <v>4.1</v>
       </c>
-      <c r="J62" s="6" t="n">
+      <c r="J62" s="5" t="n">
         <v>3.6</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="4" t="n">
+      <c r="A63" s="3" t="n">
         <v>44593</v>
       </c>
-      <c r="B63" s="5" t="n">
+      <c r="B63" s="4" t="n">
         <v>-0.961545869944198</v>
       </c>
-      <c r="C63" s="5" t="n">
+      <c r="C63" s="4" t="n">
         <v>-0.943403223335864</v>
       </c>
-      <c r="D63" s="6" t="n">
+      <c r="D63" s="5" t="n">
         <v>4.7</v>
       </c>
-      <c r="E63" s="6" t="n">
+      <c r="E63" s="5" t="n">
         <v>4.6</v>
       </c>
-      <c r="F63" s="6" t="n">
+      <c r="F63" s="5" t="n">
         <v>4.7</v>
       </c>
-      <c r="G63" s="6" t="n">
+      <c r="G63" s="5" t="n">
         <v>4.9</v>
       </c>
-      <c r="H63" s="6" t="n">
+      <c r="H63" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="I63" s="6" t="n">
+      <c r="I63" s="5" t="n">
         <v>5.4</v>
       </c>
-      <c r="J63" s="6" t="n">
+      <c r="J63" s="5" t="n">
         <v>4.8</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="4" t="n">
+      <c r="A64" s="3" t="n">
         <v>44621</v>
       </c>
-      <c r="B64" s="5" t="n">
+      <c r="B64" s="4" t="n">
         <v>-4.95150645273806</v>
       </c>
-      <c r="C64" s="5" t="n">
+      <c r="C64" s="4" t="n">
         <v>-4.85532254169908</v>
       </c>
-      <c r="D64" s="6" t="n">
+      <c r="D64" s="5" t="n">
         <v>6.7</v>
       </c>
-      <c r="E64" s="6" t="n">
+      <c r="E64" s="5" t="n">
         <v>6.7</v>
       </c>
-      <c r="F64" s="6" t="n">
+      <c r="F64" s="5" t="n">
         <v>6.6</v>
       </c>
-      <c r="G64" s="6" t="n">
+      <c r="G64" s="5" t="n">
         <v>6.8</v>
       </c>
-      <c r="H64" s="6" t="n">
+      <c r="H64" s="5" t="n">
         <v>7.2</v>
       </c>
-      <c r="I64" s="6" t="n">
+      <c r="I64" s="5" t="n">
         <v>6.8</v>
       </c>
-      <c r="J64" s="6" t="n">
+      <c r="J64" s="5" t="n">
         <v>7.4</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="4" t="n">
+      <c r="A65" s="3" t="n">
         <v>44652</v>
       </c>
-      <c r="B65" s="5" t="n">
+      <c r="B65" s="4" t="n">
         <v>-0.254129742867253</v>
       </c>
-      <c r="C65" s="5" t="n">
+      <c r="C65" s="4" t="n">
         <v>-0.249066131245192</v>
       </c>
-      <c r="D65" s="6" t="n">
+      <c r="D65" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="E65" s="6" t="n">
+      <c r="E65" s="5" t="n">
         <v>6.2</v>
       </c>
-      <c r="F65" s="6" t="n">
+      <c r="F65" s="5" t="n">
         <v>5.9</v>
       </c>
-      <c r="G65" s="6" t="n">
+      <c r="G65" s="5" t="n">
         <v>6.4</v>
       </c>
-      <c r="H65" s="6" t="n">
+      <c r="H65" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="I65" s="6" t="n">
+      <c r="I65" s="5" t="n">
         <v>5.8</v>
       </c>
-      <c r="J65" s="6" t="n">
+      <c r="J65" s="5" t="n">
         <v>5.9</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="4" t="n">
+      <c r="A66" s="3" t="n">
         <v>44682</v>
       </c>
-      <c r="B66" s="5" t="n">
+      <c r="B66" s="4" t="n">
         <v>3.0077455237278</v>
       </c>
-      <c r="C66" s="5" t="n">
+      <c r="C66" s="4" t="n">
         <v>2.94861656544635</v>
       </c>
-      <c r="D66" s="6" t="n">
+      <c r="D66" s="5" t="n">
         <v>5.1</v>
       </c>
-      <c r="E66" s="6" t="n">
+      <c r="E66" s="5" t="n">
         <v>4.8</v>
       </c>
-      <c r="F66" s="6" t="n">
+      <c r="F66" s="5" t="n">
         <v>5.3</v>
       </c>
-      <c r="G66" s="6" t="n">
+      <c r="G66" s="5" t="n">
         <v>5.6</v>
       </c>
-      <c r="H66" s="6" t="n">
+      <c r="H66" s="5" t="n">
         <v>5.3</v>
       </c>
-      <c r="I66" s="6" t="n">
+      <c r="I66" s="5" t="n">
         <v>5.2</v>
       </c>
-      <c r="J66" s="6" t="n">
+      <c r="J66" s="5" t="n">
         <v>4.9</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="4" t="n">
+      <c r="A67" s="3" t="n">
         <v>44713</v>
       </c>
-      <c r="B67" s="5" t="n">
+      <c r="B67" s="4" t="n">
         <v>14.4581228811108</v>
       </c>
-      <c r="C67" s="5" t="n">
+      <c r="C67" s="4" t="n">
         <v>14.1970261270387</v>
       </c>
-      <c r="D67" s="6" t="n">
+      <c r="D67" s="5" t="n">
         <v>5.3</v>
       </c>
-      <c r="E67" s="6" t="n">
+      <c r="E67" s="5" t="n">
         <v>5.5</v>
       </c>
-      <c r="F67" s="6" t="n">
+      <c r="F67" s="5" t="n">
         <v>5.2</v>
       </c>
-      <c r="G67" s="6" t="n">
+      <c r="G67" s="5" t="n">
         <v>5.2</v>
       </c>
-      <c r="H67" s="6" t="n">
+      <c r="H67" s="5" t="n">
         <v>4.9</v>
       </c>
-      <c r="I67" s="6" t="n">
+      <c r="I67" s="5" t="n">
         <v>5.3</v>
       </c>
-      <c r="J67" s="6" t="n">
+      <c r="J67" s="5" t="n">
         <v>5.1</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="4" t="n">
+      <c r="A68" s="3" t="n">
         <v>44743</v>
       </c>
-      <c r="B68" s="5" t="n">
+      <c r="B68" s="4" t="n">
         <v>20.0670695462151</v>
       </c>
-      <c r="C68" s="5" t="n">
+      <c r="C68" s="4" t="n">
         <v>21.8088780652586</v>
       </c>
-      <c r="D68" s="6" t="n">
+      <c r="D68" s="5" t="n">
         <v>7.4</v>
       </c>
-      <c r="E68" s="6" t="n">
+      <c r="E68" s="5" t="n">
         <v>7.4</v>
       </c>
-      <c r="F68" s="6" t="n">
+      <c r="F68" s="5" t="n">
         <v>7.5</v>
       </c>
-      <c r="G68" s="6" t="n">
+      <c r="G68" s="5" t="n">
         <v>6.7</v>
       </c>
-      <c r="H68" s="6" t="n">
+      <c r="H68" s="5" t="n">
         <v>7.4</v>
       </c>
-      <c r="I68" s="6" t="n">
+      <c r="I68" s="5" t="n">
         <v>7.3</v>
       </c>
-      <c r="J68" s="6" t="n">
+      <c r="J68" s="5" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="4" t="n">
+      <c r="A69" s="3" t="n">
         <v>44774</v>
       </c>
-      <c r="B69" s="5" t="n">
+      <c r="B69" s="4" t="n">
         <v>-0.350263055120211</v>
       </c>
-      <c r="C69" s="5" t="n">
+      <c r="C69" s="4" t="n">
         <v>-2.04785313435407</v>
       </c>
-      <c r="D69" s="6" t="n">
+      <c r="D69" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="E69" s="6" t="n">
+      <c r="E69" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="F69" s="6" t="n">
+      <c r="F69" s="5" t="n">
         <v>6.9</v>
       </c>
-      <c r="G69" s="6" t="n">
+      <c r="G69" s="5" t="n">
         <v>7.6</v>
       </c>
-      <c r="H69" s="6" t="n">
+      <c r="H69" s="5" t="n">
         <v>7.6</v>
       </c>
-      <c r="I69" s="6" t="n">
+      <c r="I69" s="5" t="n">
         <v>6.5</v>
       </c>
-      <c r="J69" s="6" t="n">
+      <c r="J69" s="5" t="n">
         <v>6.4</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="4" t="n">
+      <c r="A70" s="3" t="n">
         <v>44805</v>
       </c>
-      <c r="B70" s="5" t="n">
+      <c r="B70" s="4" t="n">
         <v>-0.35149421074445</v>
       </c>
-      <c r="C70" s="5" t="n">
+      <c r="C70" s="4" t="n">
         <v>-0.69204428445738</v>
       </c>
-      <c r="D70" s="6" t="n">
+      <c r="D70" s="5" t="n">
         <v>6.2</v>
       </c>
-      <c r="E70" s="6" t="n">
+      <c r="E70" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="F70" s="6" t="n">
+      <c r="F70" s="5" t="n">
         <v>6.3</v>
       </c>
-      <c r="G70" s="6" t="n">
+      <c r="G70" s="5" t="n">
         <v>6.1</v>
       </c>
-      <c r="H70" s="6" t="n">
+      <c r="H70" s="5" t="n">
         <v>6.8</v>
       </c>
-      <c r="I70" s="6" t="n">
+      <c r="I70" s="5" t="n">
         <v>6.1</v>
       </c>
-      <c r="J70" s="6" t="n">
+      <c r="J70" s="5" t="n">
         <v>6.1</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="4" t="n">
+      <c r="A71" s="3" t="n">
         <v>44835</v>
       </c>
-      <c r="B71" s="5" t="n">
+      <c r="B71" s="4" t="n">
         <v>0.701757265864654</v>
       </c>
-      <c r="C71" s="5" t="n">
+      <c r="C71" s="4" t="n">
         <v>0.692044284457376</v>
       </c>
-      <c r="D71" s="6" t="n">
+      <c r="D71" s="5" t="n">
         <v>6.3</v>
       </c>
-      <c r="E71" s="6" t="n">
+      <c r="E71" s="5" t="n">
         <v>6.6</v>
       </c>
-      <c r="F71" s="6" t="n">
+      <c r="F71" s="5" t="n">
         <v>6.1</v>
       </c>
-      <c r="G71" s="6" t="n">
+      <c r="G71" s="5" t="n">
         <v>6.3</v>
       </c>
-      <c r="H71" s="6" t="n">
+      <c r="H71" s="5" t="n">
         <v>6.2</v>
       </c>
-      <c r="I71" s="6" t="n">
+      <c r="I71" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="J71" s="6" t="n">
+      <c r="J71" s="5" t="n">
         <v>6.6</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="4" t="n">
+      <c r="A72" s="3" t="n">
         <v>44866</v>
       </c>
-      <c r="B72" s="5" t="n">
+      <c r="B72" s="4" t="n">
         <v>8.05804866593394</v>
       </c>
-      <c r="C72" s="5" t="n">
+      <c r="C72" s="4" t="n">
         <v>7.95120629277336</v>
       </c>
-      <c r="D72" s="6" t="n">
+      <c r="D72" s="5" t="n">
         <v>4.9</v>
       </c>
-      <c r="E72" s="6" t="n">
+      <c r="E72" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F72" s="6" t="n">
+      <c r="F72" s="5" t="n">
         <v>4.9</v>
       </c>
-      <c r="G72" s="6" t="n">
+      <c r="G72" s="5" t="n">
         <v>4.6</v>
       </c>
-      <c r="H72" s="6" t="n">
+      <c r="H72" s="5" t="n">
         <v>4.5</v>
       </c>
-      <c r="I72" s="6" t="n">
+      <c r="I72" s="5" t="n">
         <v>4.9</v>
       </c>
-      <c r="J72" s="6" t="n">
+      <c r="J72" s="5" t="n">
         <v>4.9</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="4" t="n">
+      <c r="A73" s="3" t="n">
         <v>44896</v>
       </c>
-      <c r="B73" s="5" t="n">
+      <c r="B73" s="4" t="n">
         <v>9.82384395834133</v>
       </c>
-      <c r="C73" s="5" t="n">
+      <c r="C73" s="4" t="n">
         <v>9.70457891494709</v>
       </c>
-      <c r="D73" s="6" t="n">
+      <c r="D73" s="5" t="n">
         <v>5.1</v>
       </c>
-      <c r="E73" s="6" t="n">
+      <c r="E73" s="5" t="n">
         <v>5.3</v>
       </c>
-      <c r="F73" s="6" t="n">
+      <c r="F73" s="5" t="n">
         <v>5.1</v>
       </c>
-      <c r="G73" s="6" t="n">
+      <c r="G73" s="5" t="n">
         <v>4.7</v>
       </c>
-      <c r="H73" s="6" t="n">
+      <c r="H73" s="5" t="n">
         <v>4.8</v>
       </c>
-      <c r="I73" s="6" t="n">
+      <c r="I73" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="J73" s="6" t="n">
+      <c r="J73" s="5" t="n">
         <v>4.5</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="4" t="n">
+      <c r="A74" s="3" t="n">
         <v>44927</v>
       </c>
-      <c r="B74" s="5" t="n">
+      <c r="B74" s="4" t="n">
         <v>10.2725468019821</v>
       </c>
-      <c r="C74" s="5" t="n">
+      <c r="C74" s="4" t="n">
         <v>10.1596214122922</v>
       </c>
-      <c r="D74" s="6" t="n">
+      <c r="D74" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="E74" s="6" t="n">
+      <c r="E74" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="F74" s="6" t="n">
+      <c r="F74" s="5" t="n">
         <v>6.1</v>
       </c>
-      <c r="G74" s="6" t="n">
+      <c r="G74" s="5" t="n">
         <v>6.3</v>
       </c>
-      <c r="H74" s="6" t="n">
+      <c r="H74" s="5" t="n">
         <v>5.6</v>
       </c>
-      <c r="I74" s="6" t="n">
+      <c r="I74" s="5" t="n">
         <v>6.4</v>
       </c>
-      <c r="J74" s="6" t="n">
+      <c r="J74" s="5" t="n">
         <v>5.9</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="4" t="n">
+      <c r="A75" s="3" t="n">
         <v>44958</v>
       </c>
-      <c r="B75" s="5" t="n">
+      <c r="B75" s="4" t="n">
         <v>-1.59577854386108</v>
       </c>
-      <c r="C75" s="5" t="n">
+      <c r="C75" s="4" t="n">
         <v>-1.57898017326352</v>
       </c>
-      <c r="D75" s="6" t="n">
+      <c r="D75" s="5" t="n">
         <v>6.6</v>
       </c>
-      <c r="E75" s="6" t="n">
+      <c r="E75" s="5" t="n">
         <v>6.7</v>
       </c>
-      <c r="F75" s="6" t="n">
+      <c r="F75" s="5" t="n">
         <v>6.4</v>
       </c>
-      <c r="G75" s="6" t="n">
+      <c r="G75" s="5" t="n">
         <v>7.3</v>
       </c>
-      <c r="H75" s="6" t="n">
+      <c r="H75" s="5" t="n">
         <v>7.8</v>
       </c>
-      <c r="I75" s="6" t="n">
+      <c r="I75" s="5" t="n">
         <v>6.7</v>
       </c>
-      <c r="J75" s="6" t="n">
+      <c r="J75" s="5" t="n">
         <v>5.8</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="4" t="n">
+      <c r="A76" s="3" t="n">
         <v>44986</v>
       </c>
-      <c r="B76" s="5" t="n">
+      <c r="B76" s="4" t="n">
         <v>3.94269199794579</v>
       </c>
-      <c r="C76" s="5" t="n">
+      <c r="C76" s="4" t="n">
         <v>4.15644244212506</v>
       </c>
-      <c r="D76" s="6" t="n">
+      <c r="D76" s="5" t="n">
         <v>7.7</v>
       </c>
-      <c r="E76" s="6" t="n">
+      <c r="E76" s="5" t="n">
         <v>7.8</v>
       </c>
-      <c r="F76" s="6" t="n">
+      <c r="F76" s="5" t="n">
         <v>7.8</v>
       </c>
-      <c r="G76" s="6" t="n">
+      <c r="G76" s="5" t="n">
         <v>7.3</v>
       </c>
-      <c r="H76" s="6" t="n">
+      <c r="H76" s="5" t="n">
         <v>6.2</v>
       </c>
-      <c r="I76" s="6" t="n">
+      <c r="I76" s="5" t="n">
         <v>7.9</v>
       </c>
-      <c r="J76" s="6" t="n">
+      <c r="J76" s="5" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="4" t="n">
+      <c r="A77" s="3" t="n">
         <v>45017</v>
       </c>
-      <c r="B77" s="5" t="n">
+      <c r="B77" s="4" t="n">
         <v>17.8879212602982</v>
       </c>
-      <c r="C77" s="5" t="n">
+      <c r="C77" s="4" t="n">
         <v>17.6793156577018</v>
       </c>
-      <c r="D77" s="6" t="n">
+      <c r="D77" s="5" t="n">
         <v>8.4</v>
       </c>
-      <c r="E77" s="6" t="n">
+      <c r="E77" s="5" t="n">
         <v>8.6</v>
       </c>
-      <c r="F77" s="6" t="n">
+      <c r="F77" s="5" t="n">
         <v>8.5</v>
       </c>
-      <c r="G77" s="6" t="n">
+      <c r="G77" s="5" t="n">
         <v>7.7</v>
       </c>
-      <c r="H77" s="6" t="n">
+      <c r="H77" s="5" t="n">
         <v>8.3</v>
       </c>
-      <c r="I77" s="6" t="n">
+      <c r="I77" s="5" t="n">
         <v>7.2</v>
       </c>
-      <c r="J77" s="6" t="n">
+      <c r="J77" s="5" t="n">
         <v>8.1</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="4" t="n">
+      <c r="A78" s="3" t="n">
         <v>45047</v>
       </c>
-      <c r="B78" s="5" t="n">
+      <c r="B78" s="4" t="n">
         <v>4.4264338711228</v>
       </c>
-      <c r="C78" s="5" t="n">
+      <c r="C78" s="4" t="n">
         <v>4.38026226583928</v>
       </c>
-      <c r="D78" s="6" t="n">
+      <c r="D78" s="5" t="n">
         <v>7.8</v>
       </c>
-      <c r="E78" s="6" t="n">
+      <c r="E78" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="F78" s="6" t="n">
+      <c r="F78" s="5" t="n">
         <v>7.7</v>
       </c>
-      <c r="G78" s="6" t="n">
+      <c r="G78" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="H78" s="6" t="n">
+      <c r="H78" s="5" t="n">
         <v>7.3</v>
       </c>
-      <c r="I78" s="6" t="n">
+      <c r="I78" s="5" t="n">
         <v>7.5</v>
       </c>
-      <c r="J78" s="6" t="n">
+      <c r="J78" s="5" t="n">
         <v>7.3</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="4" t="n">
+      <c r="A79" s="3" t="n">
         <v>45078</v>
       </c>
-      <c r="B79" s="5" t="n">
+      <c r="B79" s="4" t="n">
         <v>0.616651491566396</v>
       </c>
-      <c r="C79" s="5" t="n">
+      <c r="C79" s="4" t="n">
         <v>0.610378293801789</v>
       </c>
-      <c r="D79" s="6" t="n">
+      <c r="D79" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="E79" s="6" t="n">
+      <c r="E79" s="5" t="n">
         <v>5.8</v>
       </c>
-      <c r="F79" s="6" t="n">
+      <c r="F79" s="5" t="n">
         <v>5.9</v>
       </c>
-      <c r="G79" s="6" t="n">
+      <c r="G79" s="5" t="n">
         <v>6.6</v>
       </c>
-      <c r="H79" s="6" t="n">
+      <c r="H79" s="5" t="n">
         <v>6.6</v>
       </c>
-      <c r="I79" s="6" t="n">
+      <c r="I79" s="5" t="n">
         <v>5.3</v>
       </c>
-      <c r="J79" s="6" t="n">
+      <c r="J79" s="5" t="n">
         <v>6.8</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="4" t="n">
+      <c r="A80" s="3" t="n">
         <v>45108</v>
       </c>
-      <c r="B80" s="5" t="n">
+      <c r="B80" s="4" t="n">
         <v>11.0470388810097</v>
       </c>
-      <c r="C80" s="5" t="n">
+      <c r="C80" s="4" t="n">
         <v>10.9409104183826</v>
       </c>
-      <c r="D80" s="6" t="n">
+      <c r="D80" s="5" t="n">
         <v>6.3</v>
       </c>
-      <c r="E80" s="6" t="n">
+      <c r="E80" s="5" t="n">
         <v>6.2</v>
       </c>
-      <c r="F80" s="6" t="n">
+      <c r="F80" s="5" t="n">
         <v>6.4</v>
       </c>
-      <c r="G80" s="6" t="n">
+      <c r="G80" s="5" t="n">
         <v>6.1</v>
       </c>
-      <c r="H80" s="6" t="n">
+      <c r="H80" s="5" t="n">
         <v>6.3</v>
       </c>
-      <c r="I80" s="6" t="n">
+      <c r="I80" s="5" t="n">
         <v>6.3</v>
       </c>
-      <c r="J80" s="6" t="n">
+      <c r="J80" s="5" t="n">
         <v>7.8</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="4" t="n">
+      <c r="A81" s="3" t="n">
         <v>45139</v>
       </c>
-      <c r="B81" s="5" t="n">
+      <c r="B81" s="4" t="n">
         <v>27.8465417346857</v>
       </c>
-      <c r="C81" s="5" t="n">
+      <c r="C81" s="4" t="n">
         <v>28.312625591592</v>
       </c>
-      <c r="D81" s="6" t="n">
+      <c r="D81" s="5" t="n">
         <v>12.4</v>
       </c>
-      <c r="E81" s="6" t="n">
+      <c r="E81" s="5" t="n">
         <v>12.3</v>
       </c>
-      <c r="F81" s="6" t="n">
+      <c r="F81" s="5" t="n">
         <v>12.2</v>
       </c>
-      <c r="G81" s="6" t="n">
+      <c r="G81" s="5" t="n">
         <v>13.7</v>
       </c>
-      <c r="H81" s="6" t="n">
+      <c r="H81" s="5" t="n">
         <v>14.2</v>
       </c>
-      <c r="I81" s="6" t="n">
+      <c r="I81" s="5" t="n">
         <v>12.3</v>
       </c>
-      <c r="J81" s="6" t="n">
+      <c r="J81" s="5" t="n">
         <v>12.1</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="4" t="n">
+      <c r="A82" s="3" t="n">
         <v>45170</v>
       </c>
-      <c r="B82" s="5" t="n">
+      <c r="B82" s="4" t="n">
         <v>9.27817334509663</v>
       </c>
-      <c r="C82" s="5" t="n">
+      <c r="C82" s="4" t="n">
         <v>9.15671935254904</v>
       </c>
-      <c r="D82" s="6" t="n">
+      <c r="D82" s="5" t="n">
         <v>12.7</v>
       </c>
-      <c r="E82" s="6" t="n">
+      <c r="E82" s="5" t="n">
         <v>12.2</v>
       </c>
-      <c r="F82" s="6" t="n">
+      <c r="F82" s="5" t="n">
         <v>13.1</v>
       </c>
-      <c r="G82" s="6" t="n">
+      <c r="G82" s="5" t="n">
         <v>13.2</v>
       </c>
-      <c r="H82" s="6" t="n">
+      <c r="H82" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="I82" s="6" t="n">
+      <c r="I82" s="5" t="n">
         <v>13.7</v>
       </c>
-      <c r="J82" s="6" t="n">
+      <c r="J82" s="5" t="n">
         <v>14</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="4" t="n">
+      <c r="A83" s="3" t="n">
         <v>45200</v>
       </c>
-      <c r="B83" s="5" t="n">
+      <c r="B83" s="4" t="n">
         <v>9.64602661875623</v>
       </c>
-      <c r="C83" s="5" t="n">
+      <c r="C83" s="4" t="n">
         <v>13.9761942375159</v>
       </c>
-      <c r="D83" s="6" t="n">
+      <c r="D83" s="5" t="n">
         <v>8.3</v>
       </c>
-      <c r="E83" s="6" t="n">
+      <c r="E83" s="5" t="n">
         <v>8.6</v>
       </c>
-      <c r="F83" s="6" t="n">
+      <c r="F83" s="5" t="n">
         <v>8.3</v>
       </c>
-      <c r="G83" s="6" t="n">
+      <c r="G83" s="5" t="n">
         <v>7.7</v>
       </c>
-      <c r="H83" s="6" t="n">
+      <c r="H83" s="5" t="n">
         <v>7.4</v>
       </c>
-      <c r="I83" s="6" t="n">
+      <c r="I83" s="5" t="n">
         <v>7.4</v>
       </c>
-      <c r="J83" s="6" t="n">
+      <c r="J83" s="5" t="n">
         <v>8.2</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="4" t="n">
+      <c r="A84" s="3" t="n">
         <v>45231</v>
       </c>
-      <c r="B84" s="5" t="n">
+      <c r="B84" s="4" t="n">
         <v>-1.73917427118692</v>
       </c>
-      <c r="C84" s="5" t="n">
+      <c r="C84" s="4" t="n">
         <v>-1.64387263431598</v>
       </c>
-      <c r="D84" s="6" t="n">
+      <c r="D84" s="5" t="n">
         <v>12.8</v>
       </c>
-      <c r="E84" s="6" t="n">
+      <c r="E84" s="5" t="n">
         <v>12.9</v>
       </c>
-      <c r="F84" s="6" t="n">
+      <c r="F84" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="G84" s="6" t="n">
+      <c r="G84" s="5" t="n">
         <v>11.8</v>
       </c>
-      <c r="H84" s="6" t="n">
+      <c r="H84" s="5" t="n">
         <v>12.8</v>
       </c>
-      <c r="I84" s="6" t="n">
+      <c r="I84" s="5" t="n">
         <v>12.8</v>
       </c>
-      <c r="J84" s="6" t="n">
+      <c r="J84" s="5" t="n">
         <v>12</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="4" t="n">
+      <c r="A85" s="3" t="n">
         <v>45261</v>
       </c>
-      <c r="B85" s="5" t="n">
+      <c r="B85" s="4" t="n">
         <v>13.1336002061087</v>
       </c>
-      <c r="C85" s="5" t="n">
+      <c r="C85" s="4" t="n">
         <v>12.4512947872583</v>
       </c>
-      <c r="D85" s="6" t="n">
+      <c r="D85" s="5" t="n">
         <v>25.5</v>
       </c>
-      <c r="E85" s="6" t="n">
+      <c r="E85" s="5" t="n">
         <v>25.1</v>
       </c>
-      <c r="F85" s="6" t="n">
+      <c r="F85" s="5" t="n">
         <v>25.7</v>
       </c>
-      <c r="G85" s="6" t="n">
+      <c r="G85" s="5" t="n">
         <v>25.2</v>
       </c>
-      <c r="H85" s="6" t="n">
+      <c r="H85" s="5" t="n">
         <v>28.4</v>
       </c>
-      <c r="I85" s="6" t="n">
+      <c r="I85" s="5" t="n">
         <v>25.8</v>
       </c>
-      <c r="J85" s="6" t="n">
+      <c r="J85" s="5" t="n">
         <v>24.3</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="4" t="n">
+      <c r="A86" s="3" t="n">
         <v>45292</v>
       </c>
-      <c r="B86" s="5" t="n">
+      <c r="B86" s="4" t="n">
         <v>16.0722444990493</v>
       </c>
-      <c r="C86" s="5" t="n">
+      <c r="C86" s="4" t="n">
         <v>15.3453572793102</v>
       </c>
-      <c r="D86" s="6" t="n">
+      <c r="D86" s="5" t="n">
         <v>20.6</v>
       </c>
-      <c r="E86" s="6" t="n">
+      <c r="E86" s="5" t="n">
         <v>19.6</v>
       </c>
-      <c r="F86" s="6" t="n">
+      <c r="F86" s="5" t="n">
         <v>21.2</v>
       </c>
-      <c r="G86" s="6" t="n">
+      <c r="G86" s="5" t="n">
         <v>21.7</v>
       </c>
-      <c r="H86" s="6" t="n">
+      <c r="H86" s="5" t="n">
         <v>19.5</v>
       </c>
-      <c r="I86" s="6" t="n">
+      <c r="I86" s="5" t="n">
         <v>22.3</v>
       </c>
-      <c r="J86" s="6" t="n">
+      <c r="J86" s="5" t="n">
         <v>24.2</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="4" t="n">
+      <c r="A87" s="3" t="n">
         <v>45323</v>
       </c>
-      <c r="B87" s="5" t="n">
+      <c r="B87" s="4" t="n">
         <v>-12.0516024512452</v>
       </c>
-      <c r="C87" s="5" t="n">
+      <c r="C87" s="4" t="n">
         <v>-13.41292999667</v>
       </c>
-      <c r="D87" s="6" t="n">
+      <c r="D87" s="5" t="n">
         <v>13.2</v>
       </c>
-      <c r="E87" s="6" t="n">
+      <c r="E87" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="F87" s="6" t="n">
+      <c r="F87" s="5" t="n">
         <v>11.9</v>
       </c>
-      <c r="G87" s="6" t="n">
+      <c r="G87" s="5" t="n">
         <v>11.7</v>
       </c>
-      <c r="H87" s="6" t="n">
+      <c r="H87" s="5" t="n">
         <v>10.9</v>
       </c>
-      <c r="I87" s="6" t="n">
+      <c r="I87" s="5" t="n">
         <v>13.5</v>
       </c>
-      <c r="J87" s="6" t="n">
+      <c r="J87" s="5" t="n">
         <v>11.3</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="4" t="n">
+      <c r="A88" s="3" t="n">
         <v>45352</v>
       </c>
-      <c r="B88" s="5" t="n">
+      <c r="B88" s="4" t="n">
         <v>-3.50913198112701</v>
       </c>
-      <c r="C88" s="5" t="n">
+      <c r="C88" s="4" t="n">
         <v>-3.40665545636062</v>
       </c>
-      <c r="D88" s="6" t="n">
+      <c r="D88" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="E88" s="6" t="n">
+      <c r="E88" s="5" t="n">
         <v>11.5</v>
       </c>
-      <c r="F88" s="6" t="n">
+      <c r="F88" s="5" t="n">
         <v>11.3</v>
       </c>
-      <c r="G88" s="6" t="n">
+      <c r="G88" s="5" t="n">
         <v>8.8</v>
       </c>
-      <c r="H88" s="6" t="n">
+      <c r="H88" s="5" t="n">
         <v>10.3</v>
       </c>
-      <c r="I88" s="6" t="n">
+      <c r="I88" s="5" t="n">
         <v>9.3</v>
       </c>
-      <c r="J88" s="6" t="n">
+      <c r="J88" s="5" t="n">
         <v>10.5</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="4" t="n">
+      <c r="A89" s="3" t="n">
         <v>45383</v>
       </c>
-      <c r="B89" s="5" t="n">
+      <c r="B89" s="4" t="n">
         <v>3.01530381706875</v>
       </c>
-      <c r="C89" s="5" t="n">
+      <c r="C89" s="4" t="n">
         <v>2.92703823001132</v>
       </c>
-      <c r="D89" s="6" t="n">
+      <c r="D89" s="5" t="n">
         <v>8.8</v>
       </c>
-      <c r="E89" s="6" t="n">
+      <c r="E89" s="5" t="n">
         <v>9.2</v>
       </c>
-      <c r="F89" s="6" t="n">
+      <c r="F89" s="5" t="n">
         <v>8.8</v>
       </c>
-      <c r="G89" s="6" t="n">
+      <c r="G89" s="5" t="n">
         <v>9.1</v>
       </c>
-      <c r="H89" s="6" t="n">
+      <c r="H89" s="5" t="n">
         <v>6.3</v>
       </c>
-      <c r="I89" s="6" t="n">
+      <c r="I89" s="5" t="n">
         <v>8.1</v>
       </c>
-      <c r="J89" s="6" t="n">
+      <c r="J89" s="5" t="n">
         <v>8.5</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="4" t="n">
+      <c r="A90" s="3" t="n">
         <v>45413</v>
       </c>
-      <c r="B90" s="5" t="n">
+      <c r="B90" s="4" t="n">
         <v>16.8195854530306</v>
       </c>
-      <c r="C90" s="5" t="n">
+      <c r="C90" s="4" t="n">
         <v>16.3720130843409</v>
       </c>
-      <c r="D90" s="6" t="n">
+      <c r="D90" s="5" t="n">
         <v>4.2</v>
       </c>
-      <c r="E90" s="6" t="n">
+      <c r="E90" s="5" t="n">
         <v>4.3</v>
       </c>
-      <c r="F90" s="6" t="n">
+      <c r="F90" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="G90" s="6" t="n">
+      <c r="G90" s="5" t="n">
         <v>4.2</v>
       </c>
-      <c r="H90" s="6" t="n">
+      <c r="H90" s="5" t="n">
         <v>3.7</v>
       </c>
-      <c r="I90" s="6" t="n">
+      <c r="I90" s="5" t="n">
         <v>4.3</v>
       </c>
-      <c r="J90" s="6" t="n">
+      <c r="J90" s="5" t="n">
         <v>4.5</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="4" t="n">
+      <c r="A91" s="3" t="n">
         <v>45444</v>
       </c>
-      <c r="B91" s="5" t="n">
+      <c r="B91" s="4" t="n">
         <v>11.0785106468739</v>
       </c>
-      <c r="C91" s="5" t="n">
+      <c r="C91" s="4" t="n">
         <v>10.8213584640233</v>
       </c>
-      <c r="D91" s="6" t="n">
+      <c r="D91" s="5" t="n">
         <v>4.6</v>
       </c>
-      <c r="E91" s="6" t="n">
+      <c r="E91" s="5" t="n">
         <v>4.4</v>
       </c>
-      <c r="F91" s="6" t="n">
+      <c r="F91" s="5" t="n">
         <v>4.7</v>
       </c>
-      <c r="G91" s="6" t="n">
+      <c r="G91" s="5" t="n">
         <v>4.8</v>
       </c>
-      <c r="H91" s="6" t="n">
+      <c r="H91" s="5" t="n">
         <v>4.4</v>
       </c>
-      <c r="I91" s="6" t="n">
+      <c r="I91" s="5" t="n">
         <v>5.1</v>
       </c>
-      <c r="J91" s="6" t="n">
+      <c r="J91" s="5" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="4" t="n">
+      <c r="A92" s="3" t="n">
         <v>45474</v>
       </c>
-      <c r="B92" s="5" t="n">
+      <c r="B92" s="4" t="n">
         <v>-0.375234961855046</v>
       </c>
-      <c r="C92" s="5" t="n">
+      <c r="C92" s="4" t="n">
         <v>-0.36697288889624</v>
       </c>
-      <c r="D92" s="6" t="n">
+      <c r="D92" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="E92" s="6" t="n">
+      <c r="E92" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="F92" s="6" t="n">
+      <c r="F92" s="5" t="n">
         <v>3.9</v>
       </c>
-      <c r="G92" s="6" t="n">
+      <c r="G92" s="5" t="n">
         <v>3.6</v>
       </c>
-      <c r="H92" s="6" t="n">
+      <c r="H92" s="5" t="n">
         <v>4.6</v>
       </c>
-      <c r="I92" s="6" t="n">
+      <c r="I92" s="5" t="n">
         <v>4.6</v>
       </c>
-      <c r="J92" s="6" t="n">
+      <c r="J92" s="5" t="n">
         <v>4.2</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="4" t="n">
+      <c r="A93" s="3" t="n">
         <v>45505</v>
       </c>
-      <c r="B93" s="5" t="n">
+      <c r="B93" s="4" t="n">
         <v>-4.22327636232729</v>
       </c>
-      <c r="C93" s="5" t="n">
+      <c r="C93" s="4" t="n">
         <v>-4.12816589733039</v>
       </c>
-      <c r="D93" s="6" t="n">
+      <c r="D93" s="5" t="n">
         <v>4.2</v>
       </c>
-      <c r="E93" s="6" t="n">
+      <c r="E93" s="5" t="n">
         <v>4.1</v>
       </c>
-      <c r="F93" s="6" t="n">
+      <c r="F93" s="5" t="n">
         <v>3.9</v>
       </c>
-      <c r="G93" s="6" t="n">
+      <c r="G93" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="H93" s="6" t="n">
+      <c r="H93" s="5" t="n">
         <v>4.4</v>
       </c>
-      <c r="I93" s="6" t="n">
+      <c r="I93" s="5" t="n">
         <v>4.5</v>
       </c>
-      <c r="J93" s="6" t="n">
+      <c r="J93" s="5" t="n">
         <v>4.6</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="4" t="n">
+      <c r="A94" s="3" t="n">
         <v>45536</v>
       </c>
-      <c r="B94" s="5" t="n">
+      <c r="B94" s="4" t="n">
         <v>-6.06246218164349</v>
       </c>
-      <c r="C94" s="5" t="n">
+      <c r="C94" s="4" t="n">
         <v>-5.91888713903307</v>
       </c>
-      <c r="D94" s="6" t="n">
+      <c r="D94" s="5" t="n">
         <v>3.5</v>
       </c>
-      <c r="E94" s="6" t="n">
+      <c r="E94" s="5" t="n">
         <v>3.7</v>
       </c>
-      <c r="F94" s="6" t="n">
+      <c r="F94" s="5" t="n">
         <v>3.2</v>
       </c>
-      <c r="G94" s="6" t="n">
+      <c r="G94" s="5" t="n">
         <v>3.4</v>
       </c>
-      <c r="H94" s="6" t="n">
+      <c r="H94" s="5" t="n">
         <v>3.3</v>
       </c>
-      <c r="I94" s="6" t="n">
+      <c r="I94" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="J94" s="6" t="n">
+      <c r="J94" s="5" t="n">
         <v>3.7</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="4" t="n">
+      <c r="A95" s="3" t="n">
         <v>45566</v>
       </c>
-      <c r="B95" s="5" t="n">
+      <c r="B95" s="4" t="n">
         <v>-4.25596144187959</v>
       </c>
-      <c r="C95" s="5" t="n">
+      <c r="C95" s="4" t="n">
         <v>-4.14997309067527</v>
       </c>
-      <c r="D95" s="6" t="n">
+      <c r="D95" s="5" t="n">
         <v>2.7</v>
       </c>
-      <c r="E95" s="6" t="n">
+      <c r="E95" s="5" t="n">
         <v>2.8</v>
       </c>
-      <c r="F95" s="6" t="n">
+      <c r="F95" s="5" t="n">
         <v>2.6</v>
       </c>
-      <c r="G95" s="6" t="n">
+      <c r="G95" s="5" t="n">
         <v>2.6</v>
       </c>
-      <c r="H95" s="6" t="n">
+      <c r="H95" s="5" t="n">
         <v>2.6</v>
       </c>
-      <c r="I95" s="6" t="n">
+      <c r="I95" s="5" t="n">
         <v>2.2</v>
       </c>
-      <c r="J95" s="6" t="n">
+      <c r="J95" s="5" t="n">
         <v>3.2</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="4" t="n">
+      <c r="A96" s="3" t="n">
         <v>45597</v>
       </c>
-      <c r="B96" s="5" t="n">
+      <c r="B96" s="4" t="n">
         <v>-5.35842461341064</v>
       </c>
-      <c r="C96" s="5" t="n">
+      <c r="C96" s="4" t="n">
         <v>-5.21857531705702</v>
       </c>
-      <c r="D96" s="6" t="n">
+      <c r="D96" s="5" t="n">
         <v>2.4</v>
       </c>
-      <c r="E96" s="6" t="n">
+      <c r="E96" s="5" t="n">
         <v>2.6</v>
       </c>
-      <c r="F96" s="6" t="n">
+      <c r="F96" s="5" t="n">
         <v>2.3</v>
       </c>
-      <c r="G96" s="6" t="n">
+      <c r="G96" s="5" t="n">
         <v>1.9</v>
       </c>
-      <c r="H96" s="6" t="n">
+      <c r="H96" s="5" t="n">
         <v>1.8</v>
       </c>
-      <c r="I96" s="6" t="n">
+      <c r="I96" s="5" t="n">
         <v>2.1</v>
       </c>
-      <c r="J96" s="6" t="n">
+      <c r="J96" s="5" t="n">
         <v>3.3</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="4" t="n">
+      <c r="A97" s="3" t="n">
         <v>45627</v>
       </c>
-      <c r="B97" s="5" t="n">
+      <c r="B97" s="4" t="n">
         <v>10.4442663367597</v>
       </c>
-      <c r="C97" s="5" t="n">
+      <c r="C97" s="4" t="n">
         <v>9.3685484077323</v>
       </c>
-      <c r="D97" s="6" t="n">
+      <c r="D97" s="5" t="n">
         <v>2.7</v>
       </c>
-      <c r="E97" s="6" t="n">
+      <c r="E97" s="5" t="n">
         <v>2.9</v>
       </c>
-      <c r="F97" s="6" t="n">
+      <c r="F97" s="5" t="n">
         <v>2.5</v>
       </c>
-      <c r="G97" s="6" t="n">
+      <c r="G97" s="5" t="n">
         <v>2.7</v>
       </c>
-      <c r="H97" s="6" t="n">
+      <c r="H97" s="5" t="n">
         <v>2.9</v>
       </c>
-      <c r="I97" s="6" t="n">
+      <c r="I97" s="5" t="n">
         <v>2.3</v>
       </c>
-      <c r="J97" s="6" t="n">
+      <c r="J97" s="5" t="n">
         <v>2.6</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="4" t="n">
+      <c r="A98" s="3" t="n">
         <v>45658</v>
       </c>
-      <c r="B98" s="5" t="n">
+      <c r="B98" s="4" t="n">
         <v>-0.829880281469507</v>
       </c>
-      <c r="C98" s="5" t="n">
+      <c r="C98" s="4" t="n">
         <v>-0.816331063916098</v>
       </c>
-      <c r="D98" s="6" t="n">
+      <c r="D98" s="5" t="n">
         <v>2.2</v>
       </c>
-      <c r="E98" s="6" t="n">
+      <c r="E98" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F98" s="6" t="n">
+      <c r="F98" s="5" t="n">
         <v>2.3</v>
       </c>
-      <c r="G98" s="6" t="n">
+      <c r="G98" s="5" t="n">
         <v>2.6</v>
       </c>
-      <c r="H98" s="6" t="n">
+      <c r="H98" s="5" t="n">
         <v>2.5</v>
       </c>
-      <c r="I98" s="6" t="n">
+      <c r="I98" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="J98" s="6" t="n">
+      <c r="J98" s="5" t="n">
         <v>2.5</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="4" t="n">
+      <c r="A99" s="3" t="n">
         <v>45689</v>
       </c>
-      <c r="B99" s="5" t="n">
+      <c r="B99" s="4" t="n">
         <v>0.415801014866368</v>
       </c>
-      <c r="C99" s="5" t="n">
+      <c r="C99" s="4" t="n">
         <v>0.408998525152507</v>
       </c>
-      <c r="D99" s="6" t="n">
+      <c r="D99" s="5" t="n">
         <v>2.4</v>
       </c>
-      <c r="E99" s="6" t="n">
+      <c r="E99" s="5" t="n">
         <v>2.2</v>
       </c>
-      <c r="F99" s="6" t="n">
+      <c r="F99" s="5" t="n">
         <v>2.5</v>
       </c>
-      <c r="G99" s="6" t="n">
+      <c r="G99" s="5" t="n">
         <v>2.6</v>
       </c>
-      <c r="H99" s="6" t="n">
+      <c r="H99" s="5" t="n">
         <v>1.9</v>
       </c>
-      <c r="I99" s="6" t="n">
+      <c r="I99" s="5" t="n">
         <v>2.7</v>
       </c>
-      <c r="J99" s="6" t="n">
+      <c r="J99" s="5" t="n">
         <v>3.2</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="4" t="n">
+      <c r="A100" s="3" t="n">
         <v>45717</v>
       </c>
-      <c r="B100" s="5" t="n">
+      <c r="B100" s="4" t="n">
         <v>6.03805109889075</v>
       </c>
-      <c r="C100" s="5" t="n">
+      <c r="C100" s="4" t="n">
         <v>5.94234204708008</v>
       </c>
-      <c r="D100" s="6" t="n">
+      <c r="D100" s="5" t="n">
         <v>3.7</v>
       </c>
-      <c r="E100" s="6" t="n">
+      <c r="E100" s="5" t="n">
         <v>3.9</v>
       </c>
-      <c r="F100" s="6" t="n">
+      <c r="F100" s="5" t="n">
         <v>3.6</v>
       </c>
-      <c r="G100" s="6" t="n">
+      <c r="G100" s="5" t="n">
         <v>4.3</v>
       </c>
-      <c r="H100" s="6" t="n">
+      <c r="H100" s="5" t="n">
         <v>3.1</v>
       </c>
-      <c r="I100" s="6" t="n">
+      <c r="I100" s="5" t="n">
         <v>3.5</v>
       </c>
-      <c r="J100" s="6" t="n">
+      <c r="J100" s="5" t="n">
         <v>3.3</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="4" t="n">
+      <c r="A101" s="3" t="n">
         <v>45748</v>
       </c>
-      <c r="B101" s="5" t="n">
+      <c r="B101" s="4" t="n">
         <v>-9.41389909138619</v>
       </c>
-      <c r="C101" s="5" t="n">
+      <c r="C101" s="4" t="n">
         <v>-9.26214898803966</v>
       </c>
-      <c r="D101" s="6" t="n">
+      <c r="D101" s="5" t="n">
         <v>2.8</v>
       </c>
-      <c r="E101" s="6" t="n">
+      <c r="E101" s="5" t="n">
         <v>2.8</v>
       </c>
-      <c r="F101" s="6" t="n">
+      <c r="F101" s="5" t="n">
         <v>2.8</v>
       </c>
-      <c r="G101" s="6" t="n">
+      <c r="G101" s="5" t="n">
         <v>2.9</v>
       </c>
-      <c r="H101" s="6" t="n">
+      <c r="H101" s="5" t="n">
         <v>2.7</v>
       </c>
-      <c r="I101" s="6" t="n">
+      <c r="I101" s="5" t="n">
         <v>2.9</v>
       </c>
-      <c r="J101" s="6" t="n">
+      <c r="J101" s="5" t="n">
         <v>2.7</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="4" t="n">
+      <c r="A102" s="3" t="n">
         <v>45778</v>
       </c>
-      <c r="B102" s="5" t="n">
+      <c r="B102" s="4" t="n">
         <v>-0.430108189939059</v>
       </c>
-      <c r="C102" s="5" t="n">
+      <c r="C102" s="4" t="n">
         <v>-0.422833610952106</v>
       </c>
-      <c r="D102" s="6" t="n">
+      <c r="D102" s="5" t="n">
         <v>1.5</v>
       </c>
-      <c r="E102" s="6" t="n">
+      <c r="E102" s="5" t="n">
         <v>1.5</v>
       </c>
-      <c r="F102" s="6" t="n">
+      <c r="F102" s="5" t="n">
         <v>1.6</v>
       </c>
-      <c r="G102" s="6" t="n">
+      <c r="G102" s="5" t="n">
         <v>1.2</v>
       </c>
-      <c r="H102" s="6" t="n">
+      <c r="H102" s="5" t="n">
         <v>1.3</v>
       </c>
-      <c r="I102" s="6" t="n">
+      <c r="I102" s="5" t="n">
         <v>1.6</v>
       </c>
-      <c r="J102" s="6" t="n">
+      <c r="J102" s="5" t="n">
         <v>1.5</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="4" t="n">
+      <c r="A103" s="3" t="n">
         <v>45809</v>
       </c>
-      <c r="B103" s="5" t="n">
+      <c r="B103" s="4" t="n">
         <v>2.97261802652007</v>
       </c>
-      <c r="C103" s="5" t="n">
+      <c r="C103" s="4" t="n">
         <v>2.92296383149383</v>
       </c>
-      <c r="D103" s="6" t="n">
+      <c r="D103" s="5" t="n">
         <v>1.6</v>
       </c>
-      <c r="E103" s="6" t="n">
+      <c r="E103" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F103" s="6" t="n">
+      <c r="F103" s="5" t="n">
         <v>1.3</v>
       </c>
-      <c r="G103" s="6" t="n">
+      <c r="G103" s="5" t="n">
         <v>1.2</v>
       </c>
-      <c r="H103" s="6" t="n">
+      <c r="H103" s="5" t="n">
         <v>1.1</v>
       </c>
-      <c r="I103" s="6" t="n">
+      <c r="I103" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="J103" s="6" t="n">
+      <c r="J103" s="5" t="n">
         <v>1.8</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="4" t="n">
+      <c r="A104" s="3" t="n">
         <v>45839</v>
       </c>
-      <c r="B104" s="5" t="n">
+      <c r="B104" s="4" t="n">
         <v>9.56904802462539</v>
       </c>
-      <c r="C104" s="5" t="n">
+      <c r="C104" s="4" t="n">
         <v>9.41872150597011</v>
       </c>
-      <c r="D104" s="6" t="n">
+      <c r="D104" s="5" t="n">
         <v>1.9</v>
       </c>
-      <c r="E104" s="6" t="n">
+      <c r="E104" s="5" t="n">
         <v>1.9</v>
       </c>
-      <c r="F104" s="6" t="n">
+      <c r="F104" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="G104" s="6" t="n">
+      <c r="G104" s="5" t="n">
         <v>1.7</v>
       </c>
-      <c r="H104" s="6" t="n">
+      <c r="H104" s="5" t="n">
         <v>1.7</v>
       </c>
-      <c r="I104" s="6" t="n">
+      <c r="I104" s="5" t="n">
         <v>1.9</v>
       </c>
-      <c r="J104" s="6" t="n">
+      <c r="J104" s="5" t="n">
         <v>2.1</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="4" t="n">
+      <c r="A105" s="3" t="n">
         <v>45870</v>
       </c>
-      <c r="B105" s="5" t="n">
+      <c r="B105" s="4" t="n">
         <v>1.13422766039345</v>
       </c>
-      <c r="C105" s="5" t="n">
+      <c r="C105" s="4" t="n">
         <v>1.11733005981253</v>
       </c>
-      <c r="D105" s="6" t="n">
+      <c r="D105" s="5" t="n">
         <v>1.9</v>
       </c>
-      <c r="E105" s="6" t="n">
+      <c r="E105" s="5" t="n">
         <v>1.9</v>
       </c>
-      <c r="F105" s="6" t="n">
+      <c r="F105" s="5" t="n">
         <v>1.8</v>
       </c>
-      <c r="G105" s="6" t="n">
+      <c r="G105" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="H105" s="6" t="n">
+      <c r="H105" s="5" t="n">
         <v>1.7</v>
       </c>
-      <c r="I105" s="6" t="n">
+      <c r="I105" s="5" t="n">
         <v>2.1</v>
       </c>
-      <c r="J105" s="6" t="n">
+      <c r="J105" s="5" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="4" t="n">
+      <c r="A106" s="3" t="n">
         <v>45901</v>
       </c>
-      <c r="B106" s="5" t="n">
+      <c r="B106" s="4" t="n">
         <v>6.89928714869514</v>
       </c>
-      <c r="C106" s="5" t="n">
+      <c r="C106" s="4" t="n">
         <v>6.80047291140575</v>
       </c>
-      <c r="D106" s="6" t="n">
+      <c r="D106" s="5" t="n">
         <v>2.1</v>
       </c>
-      <c r="E106" s="6" t="n">
+      <c r="E106" s="5" t="n">
         <v>2.1</v>
       </c>
-      <c r="F106" s="6" t="n">
+      <c r="F106" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="G106" s="6" t="n">
+      <c r="G106" s="5" t="n">
         <v>2.2</v>
       </c>
-      <c r="H106" s="6" t="n">
+      <c r="H106" s="5" t="n">
         <v>1.8</v>
       </c>
-      <c r="I106" s="6" t="n">
+      <c r="I106" s="5" t="n">
         <v>2.2</v>
       </c>
-      <c r="J106" s="6" t="n">
+      <c r="J106" s="5" t="n">
         <v>2.4</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="4" t="n">
+      <c r="A107" s="3" t="n">
         <v>45931</v>
       </c>
-      <c r="B107" s="5" t="n">
+      <c r="B107" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="C107" s="5" t="n">
+      <c r="C107" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="D107" s="6" t="n">
+      <c r="D107" s="5" t="n">
         <v>2.3</v>
       </c>
-      <c r="E107" s="6" t="n">
+      <c r="E107" s="5" t="n">
         <v>2.4</v>
       </c>
-      <c r="F107" s="6" t="n">
+      <c r="F107" s="5" t="n">
         <v>2.3</v>
       </c>
-      <c r="G107" s="6" t="n">
+      <c r="G107" s="5" t="n">
         <v>2.1</v>
       </c>
-      <c r="H107" s="6" t="n">
+      <c r="H107" s="5" t="n">
         <v>2.2</v>
       </c>
-      <c r="I107" s="6" t="n">
+      <c r="I107" s="5" t="n">
         <v>2.3</v>
       </c>
-      <c r="J107" s="6" t="n">
+      <c r="J107" s="5" t="n">
         <v>2.4</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="4" t="n">
+      <c r="A108" s="3" t="n">
         <v>45962</v>
       </c>
-      <c r="B108" s="5" t="n">
+      <c r="B108" s="4" t="n">
         <v>-0.704228262541292</v>
       </c>
-      <c r="C108" s="5" t="n">
+      <c r="C108" s="4" t="n">
         <v>-0.694447235281105</v>
       </c>
-      <c r="D108" s="6" t="n">
+      <c r="D108" s="5" t="n">
         <v>2.5</v>
       </c>
-      <c r="E108" s="6" t="n">
+      <c r="E108" s="5" t="n">
         <v>2.5</v>
       </c>
-      <c r="F108" s="6" t="n">
+      <c r="F108" s="5" t="n">
         <v>2.5</v>
       </c>
-      <c r="G108" s="6" t="n">
+      <c r="G108" s="5" t="n">
         <v>2.3</v>
       </c>
-      <c r="H108" s="6" t="n">
+      <c r="H108" s="5" t="n">
         <v>2.4</v>
       </c>
-      <c r="I108" s="6" t="n">
+      <c r="I108" s="5" t="n">
         <v>2.8</v>
       </c>
-      <c r="J108" s="6" t="n">
+      <c r="J108" s="5" t="n">
         <v>2.3</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="4" t="n">
+      <c r="A109" s="3" t="n">
         <v>45992</v>
       </c>
-      <c r="B109" s="5" t="n">
+      <c r="B109" s="4" t="n">
         <v>6.49801197316321</v>
       </c>
-      <c r="C109" s="5" t="n">
+      <c r="C109" s="4" t="n">
         <v>6.41028861927596</v>
       </c>
-      <c r="D109" s="6" t="n">
+      <c r="D109" s="5" t="n">
         <v>2.8</v>
       </c>
-      <c r="E109" s="6" t="n">
+      <c r="E109" s="5" t="n">
         <v>2.8</v>
       </c>
-      <c r="F109" s="6" t="n">
+      <c r="F109" s="5" t="n">
         <v>2.9</v>
       </c>
-      <c r="G109" s="6" t="n">
+      <c r="G109" s="5" t="n">
         <v>2.6</v>
       </c>
-      <c r="H109" s="6" t="n">
+      <c r="H109" s="5" t="n">
         <v>3.4</v>
       </c>
-      <c r="I109" s="6" t="n">
+      <c r="I109" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="J109" s="6" t="n">
+      <c r="J109" s="5" t="n">
         <v>2.6</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="4" t="n">
+      <c r="A110" s="3" t="n">
         <v>46023</v>
       </c>
-      <c r="B110" s="5" t="n">
+      <c r="B110" s="4" t="n">
         <v>-4.05460943943499</v>
       </c>
-      <c r="C110" s="5" t="n">
+      <c r="C110" s="4" t="n">
         <v>-4.00053346136991</v>
       </c>
-      <c r="D110" s="6" t="n">
+      <c r="D110" s="5" t="n">
         <v>2.9</v>
       </c>
-      <c r="E110" s="6" t="n">
+      <c r="E110" s="5" t="n">
         <v>2.8</v>
       </c>
-      <c r="F110" s="6" t="n">
+      <c r="F110" s="5" t="n">
         <v>2.9</v>
       </c>
-      <c r="G110" s="6" t="n">
+      <c r="G110" s="5" t="n">
         <v>2.8</v>
       </c>
-      <c r="H110" s="6" t="n">
+      <c r="H110" s="5" t="n">
         <v>3.8</v>
       </c>
-      <c r="I110" s="6" t="n">
+      <c r="I110" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="J110" s="6" t="n">
+      <c r="J110" s="5" t="n">
         <v>2.9</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="4" t="n">
+      <c r="A111" s="3" t="n">
         <v>46054</v>
       </c>
-      <c r="B111" s="5" t="n">
+      <c r="B111" s="4" t="n">
         <v>-3.15262536467739</v>
       </c>
-      <c r="C111" s="5" t="n">
+      <c r="C111" s="4" t="n">
         <v>-3.10905870700311</v>
       </c>
-      <c r="D111" s="6" t="n">
+      <c r="D111" s="5" t="n">
         <v>2.9</v>
       </c>
-      <c r="E111" s="6" t="n">
+      <c r="E111" s="5" t="n">
         <v>2.6</v>
       </c>
-      <c r="F111" s="6" t="n">
+      <c r="F111" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="G111" s="6" t="n">
+      <c r="G111" s="5" t="n">
         <v>3.5</v>
       </c>
-      <c r="H111" s="6" t="n">
+      <c r="H111" s="5" t="n">
         <v>3.1</v>
       </c>
-      <c r="I111" s="6" t="n">
+      <c r="I111" s="5" t="n">
         <v>3.4</v>
       </c>
-      <c r="J111" s="6" t="n">
+      <c r="J111" s="5" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="4" t="n">
+      <c r="A112" s="3" t="n">
         <v>46082</v>
       </c>
-      <c r="B112" s="5" t="n">
+      <c r="B112" s="4" t="n">
         <v>-1.07335556431087</v>
       </c>
-      <c r="C112" s="5" t="n">
+      <c r="C112" s="4" t="n">
         <v>-1.0582109330537</v>
       </c>
-      <c r="D112" s="6" t="n">
+      <c r="D112" s="5" t="n">
         <v>3.4</v>
       </c>
-      <c r="E112" s="6" t="n">
+      <c r="E112" s="5" t="n">
         <v>3.4</v>
       </c>
-      <c r="F112" s="6" t="n">
+      <c r="F112" s="5" t="n">
         <v>3.3</v>
       </c>
-      <c r="G112" s="6" t="n">
+      <c r="G112" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="H112" s="6" t="n">
+      <c r="H112" s="5" t="n">
         <v>4.1</v>
       </c>
-      <c r="I112" s="6" t="n">
+      <c r="I112" s="5" t="n">
         <v>3.2</v>
       </c>
-      <c r="J112" s="6" t="n">
+      <c r="J112" s="5" t="n">
         <v>2.5</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="4" t="n">
+      <c r="A113" s="3" t="n">
         <v>46113</v>
       </c>
-      <c r="B113" s="5" t="n">
+      <c r="B113" s="4" t="n">
         <v>-0.722024797348702</v>
       </c>
-      <c r="C113" s="5" t="n">
+      <c r="C113" s="4" t="n">
         <v>-0.711746776886399</v>
       </c>
-      <c r="D113" s="6" t="n">
+      <c r="D113" s="5" t="n">
         <v>2.6</v>
       </c>
-      <c r="E113" s="6" t="n">
+      <c r="E113" s="5" t="n">
         <v>2.8</v>
       </c>
-      <c r="F113" s="6" t="n">
+      <c r="F113" s="5" t="n">
         <v>2.4</v>
       </c>
-      <c r="G113" s="6" t="n">
+      <c r="G113" s="5" t="n">
         <v>2.5</v>
       </c>
-      <c r="H113" s="6" t="n">
+      <c r="H113" s="5" t="n">
         <v>2.7</v>
       </c>
-      <c r="I113" s="6" t="n">
+      <c r="I113" s="5" t="n">
         <v>2.1</v>
       </c>
-      <c r="J113" s="6" t="n">
+      <c r="J113" s="5" t="n">
         <v>2.6</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B114" s="7"/>
-      <c r="C114" s="7"/>
+      <c r="A114" s="3" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B114" s="5" t="n">
+        <v>2.15062052209637</v>
+      </c>
+      <c r="C114" s="5" t="n">
+        <v>2.12022076506029</v>
+      </c>
+      <c r="D114" s="5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E114" s="5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="F114" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G114" s="5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H114" s="5" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="I114" s="5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J114" s="5" t="n">
+        <v>1.7</v>
+      </c>
     </row>
     <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B115" s="7"/>
-      <c r="C115" s="7"/>
+      <c r="B115" s="6"/>
+      <c r="C115" s="6"/>
     </row>
     <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B116" s="7"/>
-      <c r="C116" s="7"/>
+      <c r="B116" s="6"/>
+      <c r="C116" s="6"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/data/dolar-ipc.xlsx
+++ b/data/dolar-ipc.xlsx
@@ -266,9 +266,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>362880</xdr:colOff>
+      <xdr:colOff>362520</xdr:colOff>
       <xdr:row>730</xdr:row>
-      <xdr:rowOff>120600</xdr:rowOff>
+      <xdr:rowOff>120240</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -278,7 +278,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="1606680" y="118506240"/>
-          <a:ext cx="362880" cy="283320"/>
+          <a:ext cx="362520" cy="282960"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4072,8 +4072,36 @@
       </c>
     </row>
     <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B115" s="6"/>
-      <c r="C115" s="6"/>
+      <c r="A115" s="3" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B115" s="5" t="n">
+        <v>5.85365024525729</v>
+      </c>
+      <c r="C115" s="5" t="n">
+        <v>5.77409946895165</v>
+      </c>
+      <c r="D115" s="5" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="E115" s="5" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="F115" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G115" s="5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H115" s="5" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="I115" s="5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J115" s="5" t="n">
+        <v>1.6</v>
+      </c>
     </row>
     <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B116" s="6"/>
